--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/1750000/Output_8_11.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/1750000/Output_8_11.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>43449.83117659765</v>
+        <v>53681.08132787699</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5923391.754764427</v>
+        <v>5739672.253402798</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22594155.60219219</v>
+        <v>22630145.75001232</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4191225.332963197</v>
+        <v>4186498.791456414</v>
       </c>
     </row>
     <row r="11">
@@ -8670,25 +8670,25 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K11" t="n">
-        <v>202.1918359696037</v>
+        <v>208.3214547517356</v>
       </c>
       <c r="L11" t="n">
-        <v>213.5623446182285</v>
+        <v>221.1666787354324</v>
       </c>
       <c r="M11" t="n">
-        <v>205.6399266946094</v>
+        <v>214.1012135983212</v>
       </c>
       <c r="N11" t="n">
-        <v>204.3069831945809</v>
+        <v>212.9051825663978</v>
       </c>
       <c r="O11" t="n">
-        <v>206.3912516226918</v>
+        <v>214.5102874732696</v>
       </c>
       <c r="P11" t="n">
-        <v>210.9996540467268</v>
+        <v>217.9290633046618</v>
       </c>
       <c r="Q11" t="n">
-        <v>207.1112928895249</v>
+        <v>212.3149906599047</v>
       </c>
       <c r="R11" t="n">
         <v>65.71641987298243</v>
@@ -8746,28 +8746,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J12" t="n">
-        <v>119.7250323270441</v>
+        <v>122.1609165114202</v>
       </c>
       <c r="K12" t="n">
-        <v>125.6848823705854</v>
+        <v>129.8481964236088</v>
       </c>
       <c r="L12" t="n">
-        <v>122.2083892138365</v>
+        <v>127.8064787429921</v>
       </c>
       <c r="M12" t="n">
-        <v>123.0590339220183</v>
+        <v>129.5917403577182</v>
       </c>
       <c r="N12" t="n">
-        <v>111.7618535927673</v>
+        <v>118.4674613291454</v>
       </c>
       <c r="O12" t="n">
-        <v>124.6844991614256</v>
+        <v>130.8188201934042</v>
       </c>
       <c r="P12" t="n">
-        <v>119.5986526973491</v>
+        <v>124.5219861368073</v>
       </c>
       <c r="Q12" t="n">
-        <v>130.3719627652668</v>
+        <v>133.663080786811</v>
       </c>
       <c r="R12" t="n">
         <v>45.52166981132082</v>
@@ -8831,19 +8831,19 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L13" t="n">
-        <v>125.5012336582875</v>
+        <v>128.7148261097669</v>
       </c>
       <c r="M13" t="n">
-        <v>129.0322593574411</v>
+        <v>132.4205420186164</v>
       </c>
       <c r="N13" t="n">
-        <v>118.0272657767086</v>
+        <v>121.3349826493852</v>
       </c>
       <c r="O13" t="n">
-        <v>129.5355548452854</v>
+        <v>132.590766746692</v>
       </c>
       <c r="P13" t="n">
-        <v>130.0945614261968</v>
+        <v>132.7088230120157</v>
       </c>
       <c r="Q13" t="n">
         <v>65.34295837775146</v>
@@ -8907,25 +8907,25 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K14" t="n">
-        <v>202.1918359696037</v>
+        <v>208.3214547517356</v>
       </c>
       <c r="L14" t="n">
-        <v>213.5623446182285</v>
+        <v>221.1666787354324</v>
       </c>
       <c r="M14" t="n">
-        <v>205.6399266946094</v>
+        <v>214.1012135983212</v>
       </c>
       <c r="N14" t="n">
-        <v>204.3069831945809</v>
+        <v>212.9051825663978</v>
       </c>
       <c r="O14" t="n">
-        <v>206.3912516226918</v>
+        <v>214.5102874732696</v>
       </c>
       <c r="P14" t="n">
-        <v>210.9996540467268</v>
+        <v>217.9290633046618</v>
       </c>
       <c r="Q14" t="n">
-        <v>207.1112928895249</v>
+        <v>212.3149906599047</v>
       </c>
       <c r="R14" t="n">
         <v>65.71641987298243</v>
@@ -8983,28 +8983,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J15" t="n">
-        <v>119.7250323270441</v>
+        <v>122.1609165114202</v>
       </c>
       <c r="K15" t="n">
-        <v>125.6848823705854</v>
+        <v>129.8481964236088</v>
       </c>
       <c r="L15" t="n">
-        <v>122.2083892138365</v>
+        <v>127.8064787429921</v>
       </c>
       <c r="M15" t="n">
-        <v>123.0590339220183</v>
+        <v>129.5917403577182</v>
       </c>
       <c r="N15" t="n">
-        <v>111.7618535927673</v>
+        <v>118.4674613291454</v>
       </c>
       <c r="O15" t="n">
-        <v>124.6844991614256</v>
+        <v>130.8188201934042</v>
       </c>
       <c r="P15" t="n">
-        <v>119.5986526973491</v>
+        <v>124.5219861368073</v>
       </c>
       <c r="Q15" t="n">
-        <v>130.3719627652668</v>
+        <v>133.663080786811</v>
       </c>
       <c r="R15" t="n">
         <v>45.52166981132082</v>
@@ -9068,19 +9068,19 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L16" t="n">
-        <v>125.5012336582875</v>
+        <v>128.7148261097669</v>
       </c>
       <c r="M16" t="n">
-        <v>129.0322593574411</v>
+        <v>132.4205420186164</v>
       </c>
       <c r="N16" t="n">
-        <v>118.0272657767086</v>
+        <v>121.3349826493852</v>
       </c>
       <c r="O16" t="n">
-        <v>129.5355548452854</v>
+        <v>132.590766746692</v>
       </c>
       <c r="P16" t="n">
-        <v>130.0945614261968</v>
+        <v>132.7088230120157</v>
       </c>
       <c r="Q16" t="n">
         <v>65.34295837775146</v>
@@ -9144,25 +9144,25 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K17" t="n">
-        <v>202.1918359696037</v>
+        <v>208.3214547517356</v>
       </c>
       <c r="L17" t="n">
-        <v>213.5623446182285</v>
+        <v>221.1666787354324</v>
       </c>
       <c r="M17" t="n">
-        <v>205.6399266946094</v>
+        <v>214.1012135983212</v>
       </c>
       <c r="N17" t="n">
-        <v>204.3069831945809</v>
+        <v>212.9051825663978</v>
       </c>
       <c r="O17" t="n">
-        <v>206.3912516226918</v>
+        <v>214.5102874732696</v>
       </c>
       <c r="P17" t="n">
-        <v>210.9996540467268</v>
+        <v>217.9290633046618</v>
       </c>
       <c r="Q17" t="n">
-        <v>207.1112928895249</v>
+        <v>212.3149906599047</v>
       </c>
       <c r="R17" t="n">
         <v>65.71641987298243</v>
@@ -9220,28 +9220,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J18" t="n">
-        <v>119.7250323270441</v>
+        <v>122.1609165114202</v>
       </c>
       <c r="K18" t="n">
-        <v>125.6848823705854</v>
+        <v>129.8481964236088</v>
       </c>
       <c r="L18" t="n">
-        <v>122.2083892138365</v>
+        <v>127.8064787429921</v>
       </c>
       <c r="M18" t="n">
-        <v>123.0590339220183</v>
+        <v>129.5917403577182</v>
       </c>
       <c r="N18" t="n">
-        <v>111.7618535927673</v>
+        <v>118.4674613291454</v>
       </c>
       <c r="O18" t="n">
-        <v>124.6844991614256</v>
+        <v>130.8188201934042</v>
       </c>
       <c r="P18" t="n">
-        <v>119.5986526973491</v>
+        <v>124.5219861368073</v>
       </c>
       <c r="Q18" t="n">
-        <v>130.3719627652668</v>
+        <v>133.663080786811</v>
       </c>
       <c r="R18" t="n">
         <v>45.52166981132082</v>
@@ -9305,19 +9305,19 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L19" t="n">
-        <v>125.5012336582875</v>
+        <v>128.7148261097669</v>
       </c>
       <c r="M19" t="n">
-        <v>129.0322593574411</v>
+        <v>132.4205420186164</v>
       </c>
       <c r="N19" t="n">
-        <v>118.0272657767086</v>
+        <v>121.3349826493852</v>
       </c>
       <c r="O19" t="n">
-        <v>129.5355548452854</v>
+        <v>132.590766746692</v>
       </c>
       <c r="P19" t="n">
-        <v>130.0945614261968</v>
+        <v>132.7088230120157</v>
       </c>
       <c r="Q19" t="n">
         <v>65.34295837775146</v>
@@ -9381,25 +9381,25 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K20" t="n">
-        <v>202.1918359696037</v>
+        <v>208.3214547517356</v>
       </c>
       <c r="L20" t="n">
-        <v>213.5623446182285</v>
+        <v>221.1666787354324</v>
       </c>
       <c r="M20" t="n">
-        <v>205.6399266946094</v>
+        <v>214.1012135983212</v>
       </c>
       <c r="N20" t="n">
-        <v>204.3069831945809</v>
+        <v>212.9051825663978</v>
       </c>
       <c r="O20" t="n">
-        <v>206.3912516226918</v>
+        <v>214.5102874732696</v>
       </c>
       <c r="P20" t="n">
-        <v>210.9996540467268</v>
+        <v>217.9290633046618</v>
       </c>
       <c r="Q20" t="n">
-        <v>207.1112928895249</v>
+        <v>212.3149906599047</v>
       </c>
       <c r="R20" t="n">
         <v>65.71641987298243</v>
@@ -9457,28 +9457,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J21" t="n">
-        <v>119.7250323270441</v>
+        <v>122.1609165114202</v>
       </c>
       <c r="K21" t="n">
-        <v>125.6848823705854</v>
+        <v>129.8481964236088</v>
       </c>
       <c r="L21" t="n">
-        <v>122.2083892138365</v>
+        <v>127.8064787429921</v>
       </c>
       <c r="M21" t="n">
-        <v>123.0590339220183</v>
+        <v>129.5917403577182</v>
       </c>
       <c r="N21" t="n">
-        <v>111.7618535927673</v>
+        <v>118.4674613291454</v>
       </c>
       <c r="O21" t="n">
-        <v>124.6844991614256</v>
+        <v>130.8188201934042</v>
       </c>
       <c r="P21" t="n">
-        <v>119.5986526973491</v>
+        <v>124.5219861368073</v>
       </c>
       <c r="Q21" t="n">
-        <v>130.3719627652668</v>
+        <v>133.663080786811</v>
       </c>
       <c r="R21" t="n">
         <v>45.52166981132082</v>
@@ -9542,19 +9542,19 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L22" t="n">
-        <v>125.5012336582875</v>
+        <v>128.7148261097669</v>
       </c>
       <c r="M22" t="n">
-        <v>129.0322593574411</v>
+        <v>132.4205420186164</v>
       </c>
       <c r="N22" t="n">
-        <v>118.0272657767086</v>
+        <v>121.3349826493852</v>
       </c>
       <c r="O22" t="n">
-        <v>129.5355548452854</v>
+        <v>132.590766746692</v>
       </c>
       <c r="P22" t="n">
-        <v>130.0945614261968</v>
+        <v>132.7088230120157</v>
       </c>
       <c r="Q22" t="n">
         <v>65.34295837775146</v>
@@ -9618,25 +9618,25 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K23" t="n">
-        <v>202.1918359696037</v>
+        <v>208.3214547517356</v>
       </c>
       <c r="L23" t="n">
-        <v>213.5623446182285</v>
+        <v>221.1666787354324</v>
       </c>
       <c r="M23" t="n">
-        <v>205.6399266946094</v>
+        <v>214.1012135983212</v>
       </c>
       <c r="N23" t="n">
-        <v>204.3069831945809</v>
+        <v>212.9051825663978</v>
       </c>
       <c r="O23" t="n">
-        <v>206.3912516226918</v>
+        <v>214.5102874732696</v>
       </c>
       <c r="P23" t="n">
-        <v>210.9996540467268</v>
+        <v>217.9290633046618</v>
       </c>
       <c r="Q23" t="n">
-        <v>207.1112928895249</v>
+        <v>212.3149906599047</v>
       </c>
       <c r="R23" t="n">
         <v>65.71641987298243</v>
@@ -9694,28 +9694,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J24" t="n">
-        <v>119.7250323270441</v>
+        <v>122.1609165114202</v>
       </c>
       <c r="K24" t="n">
-        <v>125.6848823705854</v>
+        <v>129.8481964236088</v>
       </c>
       <c r="L24" t="n">
-        <v>122.2083892138365</v>
+        <v>127.8064787429921</v>
       </c>
       <c r="M24" t="n">
-        <v>123.0590339220183</v>
+        <v>129.5917403577182</v>
       </c>
       <c r="N24" t="n">
-        <v>111.7618535927673</v>
+        <v>118.4674613291454</v>
       </c>
       <c r="O24" t="n">
-        <v>124.6844991614256</v>
+        <v>130.8188201934042</v>
       </c>
       <c r="P24" t="n">
-        <v>119.5986526973491</v>
+        <v>124.5219861368073</v>
       </c>
       <c r="Q24" t="n">
-        <v>130.3719627652668</v>
+        <v>133.663080786811</v>
       </c>
       <c r="R24" t="n">
         <v>45.52166981132082</v>
@@ -9779,19 +9779,19 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L25" t="n">
-        <v>125.5012336582875</v>
+        <v>128.7148261097669</v>
       </c>
       <c r="M25" t="n">
-        <v>129.0322593574411</v>
+        <v>132.4205420186164</v>
       </c>
       <c r="N25" t="n">
-        <v>118.0272657767086</v>
+        <v>121.3349826493852</v>
       </c>
       <c r="O25" t="n">
-        <v>129.5355548452854</v>
+        <v>132.590766746692</v>
       </c>
       <c r="P25" t="n">
-        <v>130.0945614261968</v>
+        <v>132.7088230120157</v>
       </c>
       <c r="Q25" t="n">
         <v>65.34295837775146</v>
@@ -9855,25 +9855,25 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K26" t="n">
-        <v>202.1918359696037</v>
+        <v>208.3214547517356</v>
       </c>
       <c r="L26" t="n">
-        <v>213.5623446182285</v>
+        <v>221.1666787354324</v>
       </c>
       <c r="M26" t="n">
-        <v>205.6399266946094</v>
+        <v>214.1012135983212</v>
       </c>
       <c r="N26" t="n">
-        <v>204.3069831945809</v>
+        <v>212.9051825663978</v>
       </c>
       <c r="O26" t="n">
-        <v>206.3912516226918</v>
+        <v>214.5102874732696</v>
       </c>
       <c r="P26" t="n">
-        <v>210.9996540467268</v>
+        <v>217.9290633046618</v>
       </c>
       <c r="Q26" t="n">
-        <v>207.1112928895249</v>
+        <v>212.3149906599047</v>
       </c>
       <c r="R26" t="n">
         <v>65.71641987298243</v>
@@ -9931,28 +9931,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J27" t="n">
-        <v>119.7250323270441</v>
+        <v>122.1609165114202</v>
       </c>
       <c r="K27" t="n">
-        <v>125.6848823705854</v>
+        <v>129.8481964236088</v>
       </c>
       <c r="L27" t="n">
-        <v>122.2083892138365</v>
+        <v>127.8064787429921</v>
       </c>
       <c r="M27" t="n">
-        <v>123.0590339220183</v>
+        <v>129.5917403577182</v>
       </c>
       <c r="N27" t="n">
-        <v>111.7618535927673</v>
+        <v>118.4674613291454</v>
       </c>
       <c r="O27" t="n">
-        <v>124.6844991614256</v>
+        <v>130.8188201934042</v>
       </c>
       <c r="P27" t="n">
-        <v>119.5986526973491</v>
+        <v>124.5219861368073</v>
       </c>
       <c r="Q27" t="n">
-        <v>130.3719627652668</v>
+        <v>133.663080786811</v>
       </c>
       <c r="R27" t="n">
         <v>45.52166981132082</v>
@@ -10016,19 +10016,19 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L28" t="n">
-        <v>125.5012336582875</v>
+        <v>128.7148261097669</v>
       </c>
       <c r="M28" t="n">
-        <v>129.0322593574411</v>
+        <v>132.4205420186164</v>
       </c>
       <c r="N28" t="n">
-        <v>118.0272657767086</v>
+        <v>121.3349826493852</v>
       </c>
       <c r="O28" t="n">
-        <v>129.5355548452854</v>
+        <v>132.590766746692</v>
       </c>
       <c r="P28" t="n">
-        <v>130.0945614261968</v>
+        <v>132.7088230120157</v>
       </c>
       <c r="Q28" t="n">
         <v>65.34295837775146</v>
@@ -10092,25 +10092,25 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K29" t="n">
-        <v>202.1918359696037</v>
+        <v>208.3214547517356</v>
       </c>
       <c r="L29" t="n">
-        <v>213.5623446182285</v>
+        <v>221.1666787354324</v>
       </c>
       <c r="M29" t="n">
-        <v>205.6399266946094</v>
+        <v>214.1012135983212</v>
       </c>
       <c r="N29" t="n">
-        <v>204.3069831945809</v>
+        <v>212.9051825663978</v>
       </c>
       <c r="O29" t="n">
-        <v>206.3912516226918</v>
+        <v>214.5102874732696</v>
       </c>
       <c r="P29" t="n">
-        <v>210.9996540467268</v>
+        <v>217.9290633046618</v>
       </c>
       <c r="Q29" t="n">
-        <v>207.1112928895249</v>
+        <v>212.3149906599047</v>
       </c>
       <c r="R29" t="n">
         <v>65.71641987298243</v>
@@ -10168,28 +10168,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J30" t="n">
-        <v>119.7250323270441</v>
+        <v>122.1609165114202</v>
       </c>
       <c r="K30" t="n">
-        <v>125.6848823705854</v>
+        <v>129.8481964236088</v>
       </c>
       <c r="L30" t="n">
-        <v>122.2083892138365</v>
+        <v>127.8064787429921</v>
       </c>
       <c r="M30" t="n">
-        <v>123.0590339220183</v>
+        <v>129.5917403577182</v>
       </c>
       <c r="N30" t="n">
-        <v>111.7618535927673</v>
+        <v>118.4674613291454</v>
       </c>
       <c r="O30" t="n">
-        <v>124.6844991614256</v>
+        <v>130.8188201934042</v>
       </c>
       <c r="P30" t="n">
-        <v>119.5986526973491</v>
+        <v>124.5219861368073</v>
       </c>
       <c r="Q30" t="n">
-        <v>130.3719627652668</v>
+        <v>133.663080786811</v>
       </c>
       <c r="R30" t="n">
         <v>45.52166981132082</v>
@@ -10253,19 +10253,19 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L31" t="n">
-        <v>125.5012336582875</v>
+        <v>128.7148261097669</v>
       </c>
       <c r="M31" t="n">
-        <v>129.0322593574411</v>
+        <v>132.4205420186164</v>
       </c>
       <c r="N31" t="n">
-        <v>118.0272657767086</v>
+        <v>121.3349826493852</v>
       </c>
       <c r="O31" t="n">
-        <v>129.5355548452854</v>
+        <v>132.590766746692</v>
       </c>
       <c r="P31" t="n">
-        <v>130.0945614261968</v>
+        <v>132.7088230120157</v>
       </c>
       <c r="Q31" t="n">
         <v>65.34295837775146</v>
@@ -10329,25 +10329,25 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K32" t="n">
-        <v>202.1918359696037</v>
+        <v>208.3214547517356</v>
       </c>
       <c r="L32" t="n">
-        <v>213.5623446182285</v>
+        <v>221.1666787354324</v>
       </c>
       <c r="M32" t="n">
-        <v>205.6399266946094</v>
+        <v>214.1012135983212</v>
       </c>
       <c r="N32" t="n">
-        <v>204.3069831945809</v>
+        <v>212.9051825663978</v>
       </c>
       <c r="O32" t="n">
-        <v>206.3912516226918</v>
+        <v>214.5102874732696</v>
       </c>
       <c r="P32" t="n">
-        <v>210.9996540467268</v>
+        <v>217.9290633046618</v>
       </c>
       <c r="Q32" t="n">
-        <v>207.1112928895249</v>
+        <v>212.3149906599047</v>
       </c>
       <c r="R32" t="n">
         <v>65.71641987298243</v>
@@ -10405,28 +10405,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J33" t="n">
-        <v>119.7250323270441</v>
+        <v>122.1609165114202</v>
       </c>
       <c r="K33" t="n">
-        <v>125.6848823705854</v>
+        <v>129.8481964236088</v>
       </c>
       <c r="L33" t="n">
-        <v>122.2083892138365</v>
+        <v>127.8064787429921</v>
       </c>
       <c r="M33" t="n">
-        <v>123.0590339220183</v>
+        <v>129.5917403577182</v>
       </c>
       <c r="N33" t="n">
-        <v>111.7618535927673</v>
+        <v>118.4674613291454</v>
       </c>
       <c r="O33" t="n">
-        <v>124.6844991614256</v>
+        <v>130.8188201934042</v>
       </c>
       <c r="P33" t="n">
-        <v>119.5986526973491</v>
+        <v>124.5219861368073</v>
       </c>
       <c r="Q33" t="n">
-        <v>130.3719627652668</v>
+        <v>133.663080786811</v>
       </c>
       <c r="R33" t="n">
         <v>45.52166981132082</v>
@@ -10490,19 +10490,19 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L34" t="n">
-        <v>125.5012336582875</v>
+        <v>128.7148261097669</v>
       </c>
       <c r="M34" t="n">
-        <v>129.0322593574411</v>
+        <v>132.4205420186164</v>
       </c>
       <c r="N34" t="n">
-        <v>118.0272657767086</v>
+        <v>121.3349826493852</v>
       </c>
       <c r="O34" t="n">
-        <v>129.5355548452854</v>
+        <v>132.590766746692</v>
       </c>
       <c r="P34" t="n">
-        <v>130.0945614261968</v>
+        <v>132.7088230120157</v>
       </c>
       <c r="Q34" t="n">
         <v>65.34295837775146</v>
@@ -10566,25 +10566,25 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K35" t="n">
-        <v>202.1918359696037</v>
+        <v>208.3214547517356</v>
       </c>
       <c r="L35" t="n">
-        <v>213.5623446182285</v>
+        <v>221.1666787354324</v>
       </c>
       <c r="M35" t="n">
-        <v>205.6399266946094</v>
+        <v>214.1012135983212</v>
       </c>
       <c r="N35" t="n">
-        <v>204.3069831945809</v>
+        <v>212.9051825663978</v>
       </c>
       <c r="O35" t="n">
-        <v>206.3912516226918</v>
+        <v>214.5102874732696</v>
       </c>
       <c r="P35" t="n">
-        <v>210.9996540467268</v>
+        <v>217.9290633046618</v>
       </c>
       <c r="Q35" t="n">
-        <v>207.1112928895249</v>
+        <v>212.3149906599047</v>
       </c>
       <c r="R35" t="n">
         <v>65.71641987298243</v>
@@ -10642,28 +10642,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J36" t="n">
-        <v>119.7250323270441</v>
+        <v>122.1609165114202</v>
       </c>
       <c r="K36" t="n">
-        <v>125.6848823705854</v>
+        <v>129.8481964236088</v>
       </c>
       <c r="L36" t="n">
-        <v>122.2083892138365</v>
+        <v>127.8064787429921</v>
       </c>
       <c r="M36" t="n">
-        <v>123.0590339220183</v>
+        <v>129.5917403577182</v>
       </c>
       <c r="N36" t="n">
-        <v>111.7618535927673</v>
+        <v>118.4674613291454</v>
       </c>
       <c r="O36" t="n">
-        <v>124.6844991614256</v>
+        <v>130.8188201934042</v>
       </c>
       <c r="P36" t="n">
-        <v>119.5986526973491</v>
+        <v>124.5219861368073</v>
       </c>
       <c r="Q36" t="n">
-        <v>130.3719627652668</v>
+        <v>133.663080786811</v>
       </c>
       <c r="R36" t="n">
         <v>45.52166981132082</v>
@@ -10727,19 +10727,19 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L37" t="n">
-        <v>125.5012336582875</v>
+        <v>128.7148261097669</v>
       </c>
       <c r="M37" t="n">
-        <v>129.0322593574411</v>
+        <v>132.4205420186164</v>
       </c>
       <c r="N37" t="n">
-        <v>118.0272657767086</v>
+        <v>121.3349826493852</v>
       </c>
       <c r="O37" t="n">
-        <v>129.5355548452854</v>
+        <v>132.590766746692</v>
       </c>
       <c r="P37" t="n">
-        <v>130.0945614261968</v>
+        <v>132.7088230120157</v>
       </c>
       <c r="Q37" t="n">
         <v>65.34295837775146</v>
@@ -10803,25 +10803,25 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K38" t="n">
-        <v>202.1918359696037</v>
+        <v>208.3214547517356</v>
       </c>
       <c r="L38" t="n">
-        <v>213.5623446182285</v>
+        <v>221.1666787354324</v>
       </c>
       <c r="M38" t="n">
-        <v>205.6399266946094</v>
+        <v>214.1012135983212</v>
       </c>
       <c r="N38" t="n">
-        <v>204.3069831945809</v>
+        <v>212.9051825663978</v>
       </c>
       <c r="O38" t="n">
-        <v>206.3912516226918</v>
+        <v>214.5102874732696</v>
       </c>
       <c r="P38" t="n">
-        <v>210.9996540467268</v>
+        <v>217.9290633046618</v>
       </c>
       <c r="Q38" t="n">
-        <v>207.1112928895249</v>
+        <v>212.3149906599047</v>
       </c>
       <c r="R38" t="n">
         <v>65.71641987298243</v>
@@ -10879,28 +10879,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J39" t="n">
-        <v>119.7250323270441</v>
+        <v>122.1609165114202</v>
       </c>
       <c r="K39" t="n">
-        <v>125.6848823705854</v>
+        <v>129.8481964236088</v>
       </c>
       <c r="L39" t="n">
-        <v>122.2083892138365</v>
+        <v>127.8064787429921</v>
       </c>
       <c r="M39" t="n">
-        <v>123.0590339220183</v>
+        <v>129.5917403577182</v>
       </c>
       <c r="N39" t="n">
-        <v>111.7618535927673</v>
+        <v>118.4674613291454</v>
       </c>
       <c r="O39" t="n">
-        <v>124.6844991614256</v>
+        <v>130.8188201934042</v>
       </c>
       <c r="P39" t="n">
-        <v>119.5986526973491</v>
+        <v>124.5219861368073</v>
       </c>
       <c r="Q39" t="n">
-        <v>130.3719627652668</v>
+        <v>133.663080786811</v>
       </c>
       <c r="R39" t="n">
         <v>45.52166981132082</v>
@@ -10964,19 +10964,19 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L40" t="n">
-        <v>125.5012336582875</v>
+        <v>128.7148261097669</v>
       </c>
       <c r="M40" t="n">
-        <v>129.0322593574411</v>
+        <v>132.4205420186164</v>
       </c>
       <c r="N40" t="n">
-        <v>118.0272657767086</v>
+        <v>121.3349826493852</v>
       </c>
       <c r="O40" t="n">
-        <v>129.5355548452854</v>
+        <v>132.590766746692</v>
       </c>
       <c r="P40" t="n">
-        <v>130.0945614261968</v>
+        <v>132.7088230120157</v>
       </c>
       <c r="Q40" t="n">
         <v>65.34295837775146</v>
@@ -11040,25 +11040,25 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K41" t="n">
-        <v>202.1918359696037</v>
+        <v>208.3214547517356</v>
       </c>
       <c r="L41" t="n">
-        <v>213.5623446182285</v>
+        <v>221.1666787354324</v>
       </c>
       <c r="M41" t="n">
-        <v>205.6399266946094</v>
+        <v>214.1012135983212</v>
       </c>
       <c r="N41" t="n">
-        <v>204.3069831945809</v>
+        <v>212.9051825663978</v>
       </c>
       <c r="O41" t="n">
-        <v>206.3912516226918</v>
+        <v>214.5102874732696</v>
       </c>
       <c r="P41" t="n">
-        <v>210.9996540467268</v>
+        <v>217.9290633046618</v>
       </c>
       <c r="Q41" t="n">
-        <v>207.1112928895249</v>
+        <v>212.3149906599047</v>
       </c>
       <c r="R41" t="n">
         <v>65.71641987298243</v>
@@ -11116,28 +11116,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J42" t="n">
-        <v>119.7250323270441</v>
+        <v>122.1609165114202</v>
       </c>
       <c r="K42" t="n">
-        <v>125.6848823705854</v>
+        <v>129.8481964236088</v>
       </c>
       <c r="L42" t="n">
-        <v>122.2083892138365</v>
+        <v>127.8064787429921</v>
       </c>
       <c r="M42" t="n">
-        <v>123.0590339220183</v>
+        <v>129.5917403577182</v>
       </c>
       <c r="N42" t="n">
-        <v>111.7618535927673</v>
+        <v>118.4674613291454</v>
       </c>
       <c r="O42" t="n">
-        <v>124.6844991614256</v>
+        <v>130.8188201934042</v>
       </c>
       <c r="P42" t="n">
-        <v>119.5986526973491</v>
+        <v>124.5219861368073</v>
       </c>
       <c r="Q42" t="n">
-        <v>130.3719627652668</v>
+        <v>133.663080786811</v>
       </c>
       <c r="R42" t="n">
         <v>45.52166981132082</v>
@@ -11201,19 +11201,19 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L43" t="n">
-        <v>125.5012336582875</v>
+        <v>128.7148261097669</v>
       </c>
       <c r="M43" t="n">
-        <v>129.0322593574411</v>
+        <v>132.4205420186164</v>
       </c>
       <c r="N43" t="n">
-        <v>118.0272657767086</v>
+        <v>121.3349826493852</v>
       </c>
       <c r="O43" t="n">
-        <v>129.5355548452854</v>
+        <v>132.590766746692</v>
       </c>
       <c r="P43" t="n">
-        <v>130.0945614261968</v>
+        <v>132.7088230120157</v>
       </c>
       <c r="Q43" t="n">
         <v>65.34295837775146</v>
@@ -11277,25 +11277,25 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K44" t="n">
-        <v>202.1918359696037</v>
+        <v>208.3214547517356</v>
       </c>
       <c r="L44" t="n">
-        <v>213.5623446182285</v>
+        <v>221.1666787354324</v>
       </c>
       <c r="M44" t="n">
-        <v>205.6399266946094</v>
+        <v>214.1012135983212</v>
       </c>
       <c r="N44" t="n">
-        <v>204.3069831945809</v>
+        <v>212.9051825663978</v>
       </c>
       <c r="O44" t="n">
-        <v>206.3912516226918</v>
+        <v>214.5102874732696</v>
       </c>
       <c r="P44" t="n">
-        <v>210.9996540467268</v>
+        <v>217.9290633046618</v>
       </c>
       <c r="Q44" t="n">
-        <v>207.1112928895249</v>
+        <v>212.3149906599047</v>
       </c>
       <c r="R44" t="n">
         <v>65.71641987298243</v>
@@ -11353,28 +11353,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J45" t="n">
-        <v>119.7250323270441</v>
+        <v>122.1609165114202</v>
       </c>
       <c r="K45" t="n">
-        <v>125.6848823705854</v>
+        <v>129.8481964236088</v>
       </c>
       <c r="L45" t="n">
-        <v>122.2083892138365</v>
+        <v>127.8064787429921</v>
       </c>
       <c r="M45" t="n">
-        <v>123.0590339220183</v>
+        <v>129.5917403577182</v>
       </c>
       <c r="N45" t="n">
-        <v>111.7618535927673</v>
+        <v>118.4674613291454</v>
       </c>
       <c r="O45" t="n">
-        <v>124.6844991614256</v>
+        <v>130.8188201934042</v>
       </c>
       <c r="P45" t="n">
-        <v>119.5986526973491</v>
+        <v>124.5219861368073</v>
       </c>
       <c r="Q45" t="n">
-        <v>130.3719627652668</v>
+        <v>133.663080786811</v>
       </c>
       <c r="R45" t="n">
         <v>45.52166981132082</v>
@@ -11438,19 +11438,19 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L46" t="n">
-        <v>125.5012336582875</v>
+        <v>128.7148261097669</v>
       </c>
       <c r="M46" t="n">
-        <v>129.0322593574411</v>
+        <v>132.4205420186164</v>
       </c>
       <c r="N46" t="n">
-        <v>118.0272657767086</v>
+        <v>121.3349826493852</v>
       </c>
       <c r="O46" t="n">
-        <v>129.5355548452854</v>
+        <v>132.590766746692</v>
       </c>
       <c r="P46" t="n">
-        <v>130.0945614261968</v>
+        <v>132.7088230120157</v>
       </c>
       <c r="Q46" t="n">
         <v>65.34295837775146</v>
@@ -23230,16 +23230,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G11" t="n">
-        <v>415.1620339975471</v>
+        <v>415.2102214038314</v>
       </c>
       <c r="H11" t="n">
-        <v>338.0338222162696</v>
+        <v>338.5273214908784</v>
       </c>
       <c r="I11" t="n">
-        <v>205.0514172085969</v>
+        <v>206.909162189371</v>
       </c>
       <c r="J11" t="n">
-        <v>0.007254178733136385</v>
+        <v>4.097100052852174</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -23263,16 +23263,16 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>141.0306506044663</v>
+        <v>144.0576027644702</v>
       </c>
       <c r="S11" t="n">
-        <v>205.8137881792102</v>
+        <v>206.9118586999128</v>
       </c>
       <c r="T11" t="n">
-        <v>222.4799199158902</v>
+        <v>222.6908602868995</v>
       </c>
       <c r="U11" t="n">
-        <v>251.3343966264295</v>
+        <v>251.3382516189322</v>
       </c>
       <c r="V11" t="n">
         <v>327.7522584701349</v>
@@ -23309,13 +23309,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G12" t="n">
-        <v>137.2682341443427</v>
+        <v>137.2940166796957</v>
       </c>
       <c r="H12" t="n">
-        <v>111.5083687647983</v>
+        <v>111.757373777286</v>
       </c>
       <c r="I12" t="n">
-        <v>86.8046517193396</v>
+        <v>87.69233988828964</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -23342,16 +23342,16 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>95.48368320924691</v>
+        <v>97.08446202703757</v>
       </c>
       <c r="S12" t="n">
-        <v>170.2848220472341</v>
+        <v>170.7637213332854</v>
       </c>
       <c r="T12" t="n">
-        <v>199.8612852985952</v>
+        <v>199.9652070090748</v>
       </c>
       <c r="U12" t="n">
-        <v>225.9364292507861</v>
+        <v>225.9381254702172</v>
       </c>
       <c r="V12" t="n">
         <v>232.8005871494253</v>
@@ -23388,19 +23388,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G13" t="n">
-        <v>167.9278646043604</v>
+        <v>167.9494798159088</v>
       </c>
       <c r="H13" t="n">
-        <v>161.666024966456</v>
+        <v>161.8582038473137</v>
       </c>
       <c r="I13" t="n">
-        <v>153.552442140373</v>
+        <v>154.2024705022108</v>
       </c>
       <c r="J13" t="n">
-        <v>88.89696700191868</v>
+        <v>90.42516245839145</v>
       </c>
       <c r="K13" t="n">
-        <v>14.93670494063696</v>
+        <v>17.44799951871617</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -23418,19 +23418,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>80.87704325169439</v>
+        <v>82.6870224659892</v>
       </c>
       <c r="R13" t="n">
-        <v>174.4555225247105</v>
+        <v>175.4274210366964</v>
       </c>
       <c r="S13" t="n">
-        <v>222.9166800041854</v>
+        <v>223.2933741908973</v>
       </c>
       <c r="T13" t="n">
-        <v>227.675917297134</v>
+        <v>227.7682732010226</v>
       </c>
       <c r="U13" t="n">
-        <v>286.31558673354</v>
+        <v>286.3167657450791</v>
       </c>
       <c r="V13" t="n">
         <v>252.137643323828</v>
@@ -23467,16 +23467,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G14" t="n">
-        <v>415.1620339975471</v>
+        <v>415.2102214038314</v>
       </c>
       <c r="H14" t="n">
-        <v>338.0338222162696</v>
+        <v>338.5273214908784</v>
       </c>
       <c r="I14" t="n">
-        <v>205.0514172085969</v>
+        <v>206.909162189371</v>
       </c>
       <c r="J14" t="n">
-        <v>0.007254178733136385</v>
+        <v>4.097100052852174</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -23500,16 +23500,16 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>141.0306506044663</v>
+        <v>144.0576027644702</v>
       </c>
       <c r="S14" t="n">
-        <v>205.8137881792102</v>
+        <v>206.9118586999128</v>
       </c>
       <c r="T14" t="n">
-        <v>222.4799199158902</v>
+        <v>222.6908602868995</v>
       </c>
       <c r="U14" t="n">
-        <v>251.3343966264295</v>
+        <v>251.3382516189322</v>
       </c>
       <c r="V14" t="n">
         <v>327.7522584701349</v>
@@ -23546,13 +23546,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G15" t="n">
-        <v>137.2682341443427</v>
+        <v>137.2940166796957</v>
       </c>
       <c r="H15" t="n">
-        <v>111.5083687647983</v>
+        <v>111.757373777286</v>
       </c>
       <c r="I15" t="n">
-        <v>86.8046517193396</v>
+        <v>87.69233988828964</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -23579,16 +23579,16 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>95.48368320924691</v>
+        <v>97.08446202703757</v>
       </c>
       <c r="S15" t="n">
-        <v>170.2848220472341</v>
+        <v>170.7637213332854</v>
       </c>
       <c r="T15" t="n">
-        <v>199.8612852985952</v>
+        <v>199.9652070090748</v>
       </c>
       <c r="U15" t="n">
-        <v>225.9364292507861</v>
+        <v>225.9381254702172</v>
       </c>
       <c r="V15" t="n">
         <v>232.8005871494253</v>
@@ -23625,19 +23625,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G16" t="n">
-        <v>167.9278646043604</v>
+        <v>167.9494798159088</v>
       </c>
       <c r="H16" t="n">
-        <v>161.666024966456</v>
+        <v>161.8582038473137</v>
       </c>
       <c r="I16" t="n">
-        <v>153.552442140373</v>
+        <v>154.2024705022108</v>
       </c>
       <c r="J16" t="n">
-        <v>88.89696700191868</v>
+        <v>90.42516245839145</v>
       </c>
       <c r="K16" t="n">
-        <v>14.93670494063696</v>
+        <v>17.44799951871617</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -23655,19 +23655,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>80.87704325169439</v>
+        <v>82.6870224659892</v>
       </c>
       <c r="R16" t="n">
-        <v>174.4555225247105</v>
+        <v>175.4274210366964</v>
       </c>
       <c r="S16" t="n">
-        <v>222.9166800041854</v>
+        <v>223.2933741908973</v>
       </c>
       <c r="T16" t="n">
-        <v>227.675917297134</v>
+        <v>227.7682732010226</v>
       </c>
       <c r="U16" t="n">
-        <v>286.31558673354</v>
+        <v>286.3167657450791</v>
       </c>
       <c r="V16" t="n">
         <v>252.137643323828</v>
@@ -23704,16 +23704,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G17" t="n">
-        <v>415.1620339975471</v>
+        <v>415.2102214038314</v>
       </c>
       <c r="H17" t="n">
-        <v>338.0338222162696</v>
+        <v>338.5273214908784</v>
       </c>
       <c r="I17" t="n">
-        <v>205.0514172085969</v>
+        <v>206.909162189371</v>
       </c>
       <c r="J17" t="n">
-        <v>0.007254178733120398</v>
+        <v>4.097100052852174</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -23737,16 +23737,16 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>141.0306506044663</v>
+        <v>144.0576027644702</v>
       </c>
       <c r="S17" t="n">
-        <v>205.8137881792102</v>
+        <v>206.9118586999128</v>
       </c>
       <c r="T17" t="n">
-        <v>222.4799199158902</v>
+        <v>222.6908602868995</v>
       </c>
       <c r="U17" t="n">
-        <v>251.3343966264295</v>
+        <v>251.3382516189322</v>
       </c>
       <c r="V17" t="n">
         <v>327.7522584701349</v>
@@ -23783,13 +23783,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G18" t="n">
-        <v>137.2682341443427</v>
+        <v>137.2940166796957</v>
       </c>
       <c r="H18" t="n">
-        <v>111.5083687647983</v>
+        <v>111.757373777286</v>
       </c>
       <c r="I18" t="n">
-        <v>86.8046517193396</v>
+        <v>87.69233988828964</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -23816,16 +23816,16 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>95.48368320924691</v>
+        <v>97.08446202703757</v>
       </c>
       <c r="S18" t="n">
-        <v>170.2848220472341</v>
+        <v>170.7637213332854</v>
       </c>
       <c r="T18" t="n">
-        <v>199.8612852985952</v>
+        <v>199.9652070090748</v>
       </c>
       <c r="U18" t="n">
-        <v>225.9364292507861</v>
+        <v>225.9381254702172</v>
       </c>
       <c r="V18" t="n">
         <v>232.8005871494253</v>
@@ -23862,19 +23862,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G19" t="n">
-        <v>167.9278646043604</v>
+        <v>167.9494798159088</v>
       </c>
       <c r="H19" t="n">
-        <v>161.666024966456</v>
+        <v>161.8582038473137</v>
       </c>
       <c r="I19" t="n">
-        <v>153.552442140373</v>
+        <v>154.2024705022108</v>
       </c>
       <c r="J19" t="n">
-        <v>88.89696700191868</v>
+        <v>90.42516245839145</v>
       </c>
       <c r="K19" t="n">
-        <v>14.93670494063696</v>
+        <v>17.44799951871617</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -23892,19 +23892,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>80.87704325169439</v>
+        <v>82.6870224659892</v>
       </c>
       <c r="R19" t="n">
-        <v>174.4555225247105</v>
+        <v>175.4274210366964</v>
       </c>
       <c r="S19" t="n">
-        <v>222.9166800041854</v>
+        <v>223.2933741908973</v>
       </c>
       <c r="T19" t="n">
-        <v>227.675917297134</v>
+        <v>227.7682732010226</v>
       </c>
       <c r="U19" t="n">
-        <v>286.31558673354</v>
+        <v>286.3167657450791</v>
       </c>
       <c r="V19" t="n">
         <v>252.137643323828</v>
@@ -23941,16 +23941,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G20" t="n">
-        <v>415.1620339975471</v>
+        <v>415.2102214038314</v>
       </c>
       <c r="H20" t="n">
-        <v>338.0338222162696</v>
+        <v>338.5273214908784</v>
       </c>
       <c r="I20" t="n">
-        <v>205.0514172085969</v>
+        <v>206.909162189371</v>
       </c>
       <c r="J20" t="n">
-        <v>0.007254178733136385</v>
+        <v>4.097100052852174</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -23974,16 +23974,16 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>141.0306506044663</v>
+        <v>144.0576027644702</v>
       </c>
       <c r="S20" t="n">
-        <v>205.8137881792102</v>
+        <v>206.9118586999128</v>
       </c>
       <c r="T20" t="n">
-        <v>222.4799199158902</v>
+        <v>222.6908602868995</v>
       </c>
       <c r="U20" t="n">
-        <v>251.3343966264295</v>
+        <v>251.3382516189322</v>
       </c>
       <c r="V20" t="n">
         <v>327.7522584701349</v>
@@ -24020,13 +24020,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G21" t="n">
-        <v>137.2682341443427</v>
+        <v>137.2940166796957</v>
       </c>
       <c r="H21" t="n">
-        <v>111.5083687647983</v>
+        <v>111.757373777286</v>
       </c>
       <c r="I21" t="n">
-        <v>86.8046517193396</v>
+        <v>87.69233988828964</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -24053,16 +24053,16 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>95.48368320924691</v>
+        <v>97.08446202703757</v>
       </c>
       <c r="S21" t="n">
-        <v>170.2848220472341</v>
+        <v>170.7637213332854</v>
       </c>
       <c r="T21" t="n">
-        <v>199.8612852985952</v>
+        <v>199.9652070090748</v>
       </c>
       <c r="U21" t="n">
-        <v>225.9364292507861</v>
+        <v>225.9381254702172</v>
       </c>
       <c r="V21" t="n">
         <v>232.8005871494253</v>
@@ -24099,19 +24099,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G22" t="n">
-        <v>167.9278646043604</v>
+        <v>167.9494798159088</v>
       </c>
       <c r="H22" t="n">
-        <v>161.666024966456</v>
+        <v>161.8582038473137</v>
       </c>
       <c r="I22" t="n">
-        <v>153.552442140373</v>
+        <v>154.2024705022108</v>
       </c>
       <c r="J22" t="n">
-        <v>88.89696700191868</v>
+        <v>90.42516245839145</v>
       </c>
       <c r="K22" t="n">
-        <v>14.93670494063696</v>
+        <v>17.44799951871617</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -24129,19 +24129,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>80.87704325169439</v>
+        <v>82.6870224659892</v>
       </c>
       <c r="R22" t="n">
-        <v>174.4555225247105</v>
+        <v>175.4274210366964</v>
       </c>
       <c r="S22" t="n">
-        <v>222.9166800041854</v>
+        <v>223.2933741908973</v>
       </c>
       <c r="T22" t="n">
-        <v>227.675917297134</v>
+        <v>227.7682732010226</v>
       </c>
       <c r="U22" t="n">
-        <v>286.31558673354</v>
+        <v>286.3167657450791</v>
       </c>
       <c r="V22" t="n">
         <v>252.137643323828</v>
@@ -24178,16 +24178,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G23" t="n">
-        <v>415.1620339975471</v>
+        <v>415.2102214038314</v>
       </c>
       <c r="H23" t="n">
-        <v>338.0338222162696</v>
+        <v>338.5273214908784</v>
       </c>
       <c r="I23" t="n">
-        <v>205.0514172085969</v>
+        <v>206.909162189371</v>
       </c>
       <c r="J23" t="n">
-        <v>0.007254178733136385</v>
+        <v>4.097100052852174</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -24211,16 +24211,16 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>141.0306506044663</v>
+        <v>144.0576027644702</v>
       </c>
       <c r="S23" t="n">
-        <v>205.8137881792102</v>
+        <v>206.9118586999128</v>
       </c>
       <c r="T23" t="n">
-        <v>222.4799199158902</v>
+        <v>222.6908602868995</v>
       </c>
       <c r="U23" t="n">
-        <v>251.3343966264295</v>
+        <v>251.3382516189322</v>
       </c>
       <c r="V23" t="n">
         <v>327.7522584701349</v>
@@ -24257,13 +24257,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G24" t="n">
-        <v>137.2682341443427</v>
+        <v>137.2940166796957</v>
       </c>
       <c r="H24" t="n">
-        <v>111.5083687647983</v>
+        <v>111.757373777286</v>
       </c>
       <c r="I24" t="n">
-        <v>86.8046517193396</v>
+        <v>87.69233988828964</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -24290,16 +24290,16 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>95.48368320924691</v>
+        <v>97.08446202703757</v>
       </c>
       <c r="S24" t="n">
-        <v>170.2848220472341</v>
+        <v>170.7637213332854</v>
       </c>
       <c r="T24" t="n">
-        <v>199.8612852985952</v>
+        <v>199.9652070090748</v>
       </c>
       <c r="U24" t="n">
-        <v>225.9364292507861</v>
+        <v>225.9381254702172</v>
       </c>
       <c r="V24" t="n">
         <v>232.8005871494253</v>
@@ -24336,19 +24336,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G25" t="n">
-        <v>167.9278646043604</v>
+        <v>167.9494798159088</v>
       </c>
       <c r="H25" t="n">
-        <v>161.666024966456</v>
+        <v>161.8582038473137</v>
       </c>
       <c r="I25" t="n">
-        <v>153.552442140373</v>
+        <v>154.2024705022108</v>
       </c>
       <c r="J25" t="n">
-        <v>88.89696700191868</v>
+        <v>90.42516245839145</v>
       </c>
       <c r="K25" t="n">
-        <v>14.93670494063696</v>
+        <v>17.44799951871617</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -24366,19 +24366,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>80.87704325169439</v>
+        <v>82.6870224659892</v>
       </c>
       <c r="R25" t="n">
-        <v>174.4555225247105</v>
+        <v>175.4274210366964</v>
       </c>
       <c r="S25" t="n">
-        <v>222.9166800041854</v>
+        <v>223.2933741908973</v>
       </c>
       <c r="T25" t="n">
-        <v>227.675917297134</v>
+        <v>227.7682732010226</v>
       </c>
       <c r="U25" t="n">
-        <v>286.31558673354</v>
+        <v>286.3167657450791</v>
       </c>
       <c r="V25" t="n">
         <v>252.137643323828</v>
@@ -24415,16 +24415,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G26" t="n">
-        <v>415.1620339975471</v>
+        <v>415.2102214038314</v>
       </c>
       <c r="H26" t="n">
-        <v>338.0338222162696</v>
+        <v>338.5273214908784</v>
       </c>
       <c r="I26" t="n">
-        <v>205.0514172085969</v>
+        <v>206.909162189371</v>
       </c>
       <c r="J26" t="n">
-        <v>0.007254178733136385</v>
+        <v>4.097100052852174</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -24448,16 +24448,16 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>141.0306506044663</v>
+        <v>144.0576027644702</v>
       </c>
       <c r="S26" t="n">
-        <v>205.8137881792102</v>
+        <v>206.9118586999128</v>
       </c>
       <c r="T26" t="n">
-        <v>222.4799199158902</v>
+        <v>222.6908602868995</v>
       </c>
       <c r="U26" t="n">
-        <v>251.3343966264295</v>
+        <v>251.3382516189322</v>
       </c>
       <c r="V26" t="n">
         <v>327.7522584701349</v>
@@ -24494,13 +24494,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G27" t="n">
-        <v>137.2682341443427</v>
+        <v>137.2940166796957</v>
       </c>
       <c r="H27" t="n">
-        <v>111.5083687647983</v>
+        <v>111.757373777286</v>
       </c>
       <c r="I27" t="n">
-        <v>86.8046517193396</v>
+        <v>87.69233988828964</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -24527,16 +24527,16 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>95.48368320924691</v>
+        <v>97.08446202703757</v>
       </c>
       <c r="S27" t="n">
-        <v>170.2848220472341</v>
+        <v>170.7637213332854</v>
       </c>
       <c r="T27" t="n">
-        <v>199.8612852985952</v>
+        <v>199.9652070090748</v>
       </c>
       <c r="U27" t="n">
-        <v>225.9364292507861</v>
+        <v>225.9381254702172</v>
       </c>
       <c r="V27" t="n">
         <v>232.8005871494253</v>
@@ -24573,19 +24573,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G28" t="n">
-        <v>167.9278646043604</v>
+        <v>167.9494798159088</v>
       </c>
       <c r="H28" t="n">
-        <v>161.666024966456</v>
+        <v>161.8582038473137</v>
       </c>
       <c r="I28" t="n">
-        <v>153.552442140373</v>
+        <v>154.2024705022108</v>
       </c>
       <c r="J28" t="n">
-        <v>88.89696700191868</v>
+        <v>90.42516245839145</v>
       </c>
       <c r="K28" t="n">
-        <v>14.93670494063696</v>
+        <v>17.44799951871617</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -24603,19 +24603,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>80.87704325169439</v>
+        <v>82.6870224659892</v>
       </c>
       <c r="R28" t="n">
-        <v>174.4555225247105</v>
+        <v>175.4274210366964</v>
       </c>
       <c r="S28" t="n">
-        <v>222.9166800041854</v>
+        <v>223.2933741908973</v>
       </c>
       <c r="T28" t="n">
-        <v>227.675917297134</v>
+        <v>227.7682732010226</v>
       </c>
       <c r="U28" t="n">
-        <v>286.31558673354</v>
+        <v>286.3167657450791</v>
       </c>
       <c r="V28" t="n">
         <v>252.137643323828</v>
@@ -24652,16 +24652,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G29" t="n">
-        <v>415.1620339975471</v>
+        <v>415.2102214038314</v>
       </c>
       <c r="H29" t="n">
-        <v>338.0338222162696</v>
+        <v>338.5273214908784</v>
       </c>
       <c r="I29" t="n">
-        <v>205.0514172085969</v>
+        <v>206.909162189371</v>
       </c>
       <c r="J29" t="n">
-        <v>0.007254178733136385</v>
+        <v>4.097100052852174</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -24685,16 +24685,16 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>141.0306506044663</v>
+        <v>144.0576027644702</v>
       </c>
       <c r="S29" t="n">
-        <v>205.8137881792102</v>
+        <v>206.9118586999128</v>
       </c>
       <c r="T29" t="n">
-        <v>222.4799199158902</v>
+        <v>222.6908602868995</v>
       </c>
       <c r="U29" t="n">
-        <v>251.3343966264295</v>
+        <v>251.3382516189322</v>
       </c>
       <c r="V29" t="n">
         <v>327.7522584701349</v>
@@ -24731,13 +24731,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G30" t="n">
-        <v>137.2682341443427</v>
+        <v>137.2940166796957</v>
       </c>
       <c r="H30" t="n">
-        <v>111.5083687647983</v>
+        <v>111.757373777286</v>
       </c>
       <c r="I30" t="n">
-        <v>86.8046517193396</v>
+        <v>87.69233988828964</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -24764,16 +24764,16 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>95.48368320924691</v>
+        <v>97.08446202703757</v>
       </c>
       <c r="S30" t="n">
-        <v>170.2848220472341</v>
+        <v>170.7637213332854</v>
       </c>
       <c r="T30" t="n">
-        <v>199.8612852985952</v>
+        <v>199.9652070090748</v>
       </c>
       <c r="U30" t="n">
-        <v>225.9364292507861</v>
+        <v>225.9381254702172</v>
       </c>
       <c r="V30" t="n">
         <v>232.8005871494253</v>
@@ -24810,19 +24810,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G31" t="n">
-        <v>167.9278646043604</v>
+        <v>167.9494798159088</v>
       </c>
       <c r="H31" t="n">
-        <v>161.666024966456</v>
+        <v>161.8582038473137</v>
       </c>
       <c r="I31" t="n">
-        <v>153.552442140373</v>
+        <v>154.2024705022108</v>
       </c>
       <c r="J31" t="n">
-        <v>88.89696700191868</v>
+        <v>90.42516245839145</v>
       </c>
       <c r="K31" t="n">
-        <v>14.93670494063696</v>
+        <v>17.44799951871617</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -24840,19 +24840,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>80.87704325169439</v>
+        <v>82.6870224659892</v>
       </c>
       <c r="R31" t="n">
-        <v>174.4555225247105</v>
+        <v>175.4274210366964</v>
       </c>
       <c r="S31" t="n">
-        <v>222.9166800041854</v>
+        <v>223.2933741908973</v>
       </c>
       <c r="T31" t="n">
-        <v>227.675917297134</v>
+        <v>227.7682732010226</v>
       </c>
       <c r="U31" t="n">
-        <v>286.31558673354</v>
+        <v>286.3167657450791</v>
       </c>
       <c r="V31" t="n">
         <v>252.137643323828</v>
@@ -24889,16 +24889,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G32" t="n">
-        <v>415.1620339975471</v>
+        <v>415.2102214038314</v>
       </c>
       <c r="H32" t="n">
-        <v>338.0338222162696</v>
+        <v>338.5273214908784</v>
       </c>
       <c r="I32" t="n">
-        <v>205.0514172085969</v>
+        <v>206.909162189371</v>
       </c>
       <c r="J32" t="n">
-        <v>0.007254178733136385</v>
+        <v>4.097100052852173</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -24922,16 +24922,16 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>141.0306506044663</v>
+        <v>144.0576027644702</v>
       </c>
       <c r="S32" t="n">
-        <v>205.8137881792102</v>
+        <v>206.9118586999128</v>
       </c>
       <c r="T32" t="n">
-        <v>222.4799199158902</v>
+        <v>222.6908602868995</v>
       </c>
       <c r="U32" t="n">
-        <v>251.3343966264295</v>
+        <v>251.3382516189322</v>
       </c>
       <c r="V32" t="n">
         <v>327.7522584701349</v>
@@ -24968,13 +24968,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G33" t="n">
-        <v>137.2682341443427</v>
+        <v>137.2940166796957</v>
       </c>
       <c r="H33" t="n">
-        <v>111.5083687647983</v>
+        <v>111.757373777286</v>
       </c>
       <c r="I33" t="n">
-        <v>86.8046517193396</v>
+        <v>87.69233988828964</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -25001,16 +25001,16 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>95.48368320924691</v>
+        <v>97.08446202703757</v>
       </c>
       <c r="S33" t="n">
-        <v>170.2848220472341</v>
+        <v>170.7637213332854</v>
       </c>
       <c r="T33" t="n">
-        <v>199.8612852985952</v>
+        <v>199.9652070090748</v>
       </c>
       <c r="U33" t="n">
-        <v>225.9364292507861</v>
+        <v>225.9381254702172</v>
       </c>
       <c r="V33" t="n">
         <v>232.8005871494253</v>
@@ -25047,19 +25047,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G34" t="n">
-        <v>167.9278646043604</v>
+        <v>167.9494798159088</v>
       </c>
       <c r="H34" t="n">
-        <v>161.666024966456</v>
+        <v>161.8582038473137</v>
       </c>
       <c r="I34" t="n">
-        <v>153.552442140373</v>
+        <v>154.2024705022108</v>
       </c>
       <c r="J34" t="n">
-        <v>88.89696700191868</v>
+        <v>90.42516245839145</v>
       </c>
       <c r="K34" t="n">
-        <v>14.93670494063696</v>
+        <v>17.44799951871617</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -25077,19 +25077,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>80.87704325169439</v>
+        <v>82.6870224659892</v>
       </c>
       <c r="R34" t="n">
-        <v>174.4555225247105</v>
+        <v>175.4274210366964</v>
       </c>
       <c r="S34" t="n">
-        <v>222.9166800041854</v>
+        <v>223.2933741908973</v>
       </c>
       <c r="T34" t="n">
-        <v>227.675917297134</v>
+        <v>227.7682732010226</v>
       </c>
       <c r="U34" t="n">
-        <v>286.31558673354</v>
+        <v>286.3167657450791</v>
       </c>
       <c r="V34" t="n">
         <v>252.137643323828</v>
@@ -25126,16 +25126,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G35" t="n">
-        <v>415.1620339975471</v>
+        <v>415.2102214038314</v>
       </c>
       <c r="H35" t="n">
-        <v>338.0338222162696</v>
+        <v>338.5273214908784</v>
       </c>
       <c r="I35" t="n">
-        <v>205.0514172085969</v>
+        <v>206.909162189371</v>
       </c>
       <c r="J35" t="n">
-        <v>0.007254178733120398</v>
+        <v>4.097100052852174</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -25159,16 +25159,16 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>141.0306506044663</v>
+        <v>144.0576027644702</v>
       </c>
       <c r="S35" t="n">
-        <v>205.8137881792102</v>
+        <v>206.9118586999128</v>
       </c>
       <c r="T35" t="n">
-        <v>222.4799199158902</v>
+        <v>222.6908602868995</v>
       </c>
       <c r="U35" t="n">
-        <v>251.3343966264295</v>
+        <v>251.3382516189322</v>
       </c>
       <c r="V35" t="n">
         <v>327.7522584701349</v>
@@ -25205,13 +25205,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G36" t="n">
-        <v>137.2682341443427</v>
+        <v>137.2940166796957</v>
       </c>
       <c r="H36" t="n">
-        <v>111.5083687647983</v>
+        <v>111.757373777286</v>
       </c>
       <c r="I36" t="n">
-        <v>86.8046517193396</v>
+        <v>87.69233988828964</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -25238,16 +25238,16 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>95.48368320924691</v>
+        <v>97.08446202703757</v>
       </c>
       <c r="S36" t="n">
-        <v>170.2848220472341</v>
+        <v>170.7637213332854</v>
       </c>
       <c r="T36" t="n">
-        <v>199.8612852985952</v>
+        <v>199.9652070090748</v>
       </c>
       <c r="U36" t="n">
-        <v>225.9364292507861</v>
+        <v>225.9381254702172</v>
       </c>
       <c r="V36" t="n">
         <v>232.8005871494253</v>
@@ -25284,19 +25284,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G37" t="n">
-        <v>167.9278646043604</v>
+        <v>167.9494798159088</v>
       </c>
       <c r="H37" t="n">
-        <v>161.666024966456</v>
+        <v>161.8582038473137</v>
       </c>
       <c r="I37" t="n">
-        <v>153.552442140373</v>
+        <v>154.2024705022108</v>
       </c>
       <c r="J37" t="n">
-        <v>88.89696700191868</v>
+        <v>90.42516245839145</v>
       </c>
       <c r="K37" t="n">
-        <v>14.93670494063696</v>
+        <v>17.44799951871617</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -25314,19 +25314,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>80.87704325169439</v>
+        <v>82.6870224659892</v>
       </c>
       <c r="R37" t="n">
-        <v>174.4555225247105</v>
+        <v>175.4274210366964</v>
       </c>
       <c r="S37" t="n">
-        <v>222.9166800041854</v>
+        <v>223.2933741908973</v>
       </c>
       <c r="T37" t="n">
-        <v>227.675917297134</v>
+        <v>227.7682732010226</v>
       </c>
       <c r="U37" t="n">
-        <v>286.31558673354</v>
+        <v>286.3167657450791</v>
       </c>
       <c r="V37" t="n">
         <v>252.137643323828</v>
@@ -25363,16 +25363,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G38" t="n">
-        <v>415.1620339975471</v>
+        <v>415.2102214038314</v>
       </c>
       <c r="H38" t="n">
-        <v>338.0338222162696</v>
+        <v>338.5273214908784</v>
       </c>
       <c r="I38" t="n">
-        <v>205.0514172085969</v>
+        <v>206.909162189371</v>
       </c>
       <c r="J38" t="n">
-        <v>0.007254178733136385</v>
+        <v>4.097100052852174</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -25396,16 +25396,16 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>141.0306506044663</v>
+        <v>144.0576027644702</v>
       </c>
       <c r="S38" t="n">
-        <v>205.8137881792102</v>
+        <v>206.9118586999128</v>
       </c>
       <c r="T38" t="n">
-        <v>222.4799199158902</v>
+        <v>222.6908602868995</v>
       </c>
       <c r="U38" t="n">
-        <v>251.3343966264295</v>
+        <v>251.3382516189322</v>
       </c>
       <c r="V38" t="n">
         <v>327.7522584701349</v>
@@ -25442,13 +25442,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G39" t="n">
-        <v>137.2682341443427</v>
+        <v>137.2940166796957</v>
       </c>
       <c r="H39" t="n">
-        <v>111.5083687647983</v>
+        <v>111.757373777286</v>
       </c>
       <c r="I39" t="n">
-        <v>86.8046517193396</v>
+        <v>87.69233988828964</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -25475,16 +25475,16 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>95.48368320924691</v>
+        <v>97.08446202703757</v>
       </c>
       <c r="S39" t="n">
-        <v>170.2848220472341</v>
+        <v>170.7637213332854</v>
       </c>
       <c r="T39" t="n">
-        <v>199.8612852985952</v>
+        <v>199.9652070090748</v>
       </c>
       <c r="U39" t="n">
-        <v>225.9364292507861</v>
+        <v>225.9381254702172</v>
       </c>
       <c r="V39" t="n">
         <v>232.8005871494253</v>
@@ -25521,19 +25521,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G40" t="n">
-        <v>167.9278646043604</v>
+        <v>167.9494798159088</v>
       </c>
       <c r="H40" t="n">
-        <v>161.666024966456</v>
+        <v>161.8582038473137</v>
       </c>
       <c r="I40" t="n">
-        <v>153.552442140373</v>
+        <v>154.2024705022108</v>
       </c>
       <c r="J40" t="n">
-        <v>88.89696700191868</v>
+        <v>90.42516245839145</v>
       </c>
       <c r="K40" t="n">
-        <v>14.93670494063696</v>
+        <v>17.44799951871617</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -25551,19 +25551,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>80.87704325169439</v>
+        <v>82.6870224659892</v>
       </c>
       <c r="R40" t="n">
-        <v>174.4555225247105</v>
+        <v>175.4274210366964</v>
       </c>
       <c r="S40" t="n">
-        <v>222.9166800041854</v>
+        <v>223.2933741908973</v>
       </c>
       <c r="T40" t="n">
-        <v>227.675917297134</v>
+        <v>227.7682732010226</v>
       </c>
       <c r="U40" t="n">
-        <v>286.31558673354</v>
+        <v>286.3167657450791</v>
       </c>
       <c r="V40" t="n">
         <v>252.137643323828</v>
@@ -25600,16 +25600,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G41" t="n">
-        <v>415.1620339975471</v>
+        <v>415.2102214038314</v>
       </c>
       <c r="H41" t="n">
-        <v>338.0338222162696</v>
+        <v>338.5273214908784</v>
       </c>
       <c r="I41" t="n">
-        <v>205.0514172085969</v>
+        <v>206.909162189371</v>
       </c>
       <c r="J41" t="n">
-        <v>0.007254178733120398</v>
+        <v>4.097100052852174</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -25633,16 +25633,16 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>141.0306506044663</v>
+        <v>144.0576027644702</v>
       </c>
       <c r="S41" t="n">
-        <v>205.8137881792102</v>
+        <v>206.9118586999128</v>
       </c>
       <c r="T41" t="n">
-        <v>222.4799199158902</v>
+        <v>222.6908602868995</v>
       </c>
       <c r="U41" t="n">
-        <v>251.3343966264295</v>
+        <v>251.3382516189322</v>
       </c>
       <c r="V41" t="n">
         <v>327.7522584701349</v>
@@ -25679,13 +25679,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G42" t="n">
-        <v>137.2682341443427</v>
+        <v>137.2940166796957</v>
       </c>
       <c r="H42" t="n">
-        <v>111.5083687647983</v>
+        <v>111.757373777286</v>
       </c>
       <c r="I42" t="n">
-        <v>86.8046517193396</v>
+        <v>87.69233988828964</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -25712,16 +25712,16 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>95.48368320924691</v>
+        <v>97.08446202703757</v>
       </c>
       <c r="S42" t="n">
-        <v>170.2848220472341</v>
+        <v>170.7637213332854</v>
       </c>
       <c r="T42" t="n">
-        <v>199.8612852985952</v>
+        <v>199.9652070090748</v>
       </c>
       <c r="U42" t="n">
-        <v>225.9364292507861</v>
+        <v>225.9381254702172</v>
       </c>
       <c r="V42" t="n">
         <v>232.8005871494253</v>
@@ -25758,19 +25758,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G43" t="n">
-        <v>167.9278646043604</v>
+        <v>167.9494798159088</v>
       </c>
       <c r="H43" t="n">
-        <v>161.666024966456</v>
+        <v>161.8582038473137</v>
       </c>
       <c r="I43" t="n">
-        <v>153.552442140373</v>
+        <v>154.2024705022108</v>
       </c>
       <c r="J43" t="n">
-        <v>88.89696700191868</v>
+        <v>90.42516245839145</v>
       </c>
       <c r="K43" t="n">
-        <v>14.93670494063696</v>
+        <v>17.44799951871617</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -25788,19 +25788,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>80.87704325169439</v>
+        <v>82.6870224659892</v>
       </c>
       <c r="R43" t="n">
-        <v>174.4555225247105</v>
+        <v>175.4274210366964</v>
       </c>
       <c r="S43" t="n">
-        <v>222.9166800041854</v>
+        <v>223.2933741908973</v>
       </c>
       <c r="T43" t="n">
-        <v>227.675917297134</v>
+        <v>227.7682732010226</v>
       </c>
       <c r="U43" t="n">
-        <v>286.31558673354</v>
+        <v>286.3167657450791</v>
       </c>
       <c r="V43" t="n">
         <v>252.137643323828</v>
@@ -25837,16 +25837,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G44" t="n">
-        <v>415.1620339975471</v>
+        <v>415.2102214038314</v>
       </c>
       <c r="H44" t="n">
-        <v>338.0338222162696</v>
+        <v>338.5273214908784</v>
       </c>
       <c r="I44" t="n">
-        <v>205.0514172085969</v>
+        <v>206.909162189371</v>
       </c>
       <c r="J44" t="n">
-        <v>0.007254178733120398</v>
+        <v>4.097100052852174</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -25870,16 +25870,16 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>141.0306506044663</v>
+        <v>144.0576027644702</v>
       </c>
       <c r="S44" t="n">
-        <v>205.8137881792102</v>
+        <v>206.9118586999128</v>
       </c>
       <c r="T44" t="n">
-        <v>222.4799199158902</v>
+        <v>222.6908602868995</v>
       </c>
       <c r="U44" t="n">
-        <v>251.3343966264295</v>
+        <v>251.3382516189322</v>
       </c>
       <c r="V44" t="n">
         <v>327.7522584701349</v>
@@ -25916,13 +25916,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G45" t="n">
-        <v>137.2682341443427</v>
+        <v>137.2940166796957</v>
       </c>
       <c r="H45" t="n">
-        <v>111.5083687647983</v>
+        <v>111.757373777286</v>
       </c>
       <c r="I45" t="n">
-        <v>86.8046517193396</v>
+        <v>87.69233988828964</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -25949,16 +25949,16 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>95.48368320924691</v>
+        <v>97.08446202703757</v>
       </c>
       <c r="S45" t="n">
-        <v>170.2848220472341</v>
+        <v>170.7637213332854</v>
       </c>
       <c r="T45" t="n">
-        <v>199.8612852985952</v>
+        <v>199.9652070090748</v>
       </c>
       <c r="U45" t="n">
-        <v>225.9364292507861</v>
+        <v>225.9381254702172</v>
       </c>
       <c r="V45" t="n">
         <v>232.8005871494253</v>
@@ -25995,19 +25995,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G46" t="n">
-        <v>167.9278646043604</v>
+        <v>167.9494798159088</v>
       </c>
       <c r="H46" t="n">
-        <v>161.666024966456</v>
+        <v>161.8582038473137</v>
       </c>
       <c r="I46" t="n">
-        <v>153.552442140373</v>
+        <v>154.2024705022108</v>
       </c>
       <c r="J46" t="n">
-        <v>88.89696700191868</v>
+        <v>90.42516245839145</v>
       </c>
       <c r="K46" t="n">
-        <v>14.93670494063696</v>
+        <v>17.44799951871617</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -26025,19 +26025,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>80.87704325169439</v>
+        <v>82.6870224659892</v>
       </c>
       <c r="R46" t="n">
-        <v>174.4555225247105</v>
+        <v>175.4274210366964</v>
       </c>
       <c r="S46" t="n">
-        <v>222.9166800041854</v>
+        <v>223.2933741908973</v>
       </c>
       <c r="T46" t="n">
-        <v>227.675917297134</v>
+        <v>227.7682732010226</v>
       </c>
       <c r="U46" t="n">
-        <v>286.31558673354</v>
+        <v>286.3167657450791</v>
       </c>
       <c r="V46" t="n">
         <v>252.137643323828</v>
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>363234.8306278678</v>
+        <v>362690.1117024551</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>363234.8306278678</v>
+        <v>362690.1117024551</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>363234.8306278678</v>
+        <v>362690.1117024551</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>363234.8306278678</v>
+        <v>362690.1117024551</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>363234.8306278678</v>
+        <v>362690.1117024551</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>363234.8306278678</v>
+        <v>362690.1117024551</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>363234.8306278678</v>
+        <v>362690.1117024551</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>363234.8306278678</v>
+        <v>362690.1117024551</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>363234.8306278678</v>
+        <v>362690.1117024551</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>363234.8306278678</v>
+        <v>362690.1117024551</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>363234.8306278678</v>
+        <v>362690.1117024551</v>
       </c>
     </row>
     <row r="16">
@@ -26190,7 +26190,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>363234.8306278678</v>
+        <v>362690.1117024551</v>
       </c>
     </row>
   </sheetData>
@@ -26270,40 +26270,40 @@
         <v>59129.07304229552</v>
       </c>
       <c r="E2" t="n">
-        <v>60337.74711017842</v>
+        <v>60007.83742182715</v>
       </c>
       <c r="F2" t="n">
-        <v>60337.74711017842</v>
+        <v>60007.83742182716</v>
       </c>
       <c r="G2" t="n">
-        <v>60337.74711017842</v>
+        <v>60007.83742182716</v>
       </c>
       <c r="H2" t="n">
-        <v>60337.74711017842</v>
+        <v>60007.83742182716</v>
       </c>
       <c r="I2" t="n">
-        <v>60337.74711017843</v>
+        <v>60007.83742182716</v>
       </c>
       <c r="J2" t="n">
-        <v>60337.74711017843</v>
+        <v>60007.83742182716</v>
       </c>
       <c r="K2" t="n">
-        <v>60337.74711017842</v>
+        <v>60007.83742182717</v>
       </c>
       <c r="L2" t="n">
-        <v>60337.74711017842</v>
+        <v>60007.83742182716</v>
       </c>
       <c r="M2" t="n">
-        <v>60337.74711017842</v>
+        <v>60007.83742182715</v>
       </c>
       <c r="N2" t="n">
-        <v>60337.74711017842</v>
+        <v>60007.83742182715</v>
       </c>
       <c r="O2" t="n">
-        <v>60337.74711017843</v>
+        <v>60007.83742182715</v>
       </c>
       <c r="P2" t="n">
-        <v>60337.74711017843</v>
+        <v>60007.83742182715</v>
       </c>
     </row>
     <row r="3">
@@ -26322,7 +26322,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>28119.10499999996</v>
+        <v>18489.0206907146</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>43002.96221257856</v>
+        <v>41731.10116290394</v>
       </c>
       <c r="C4" t="n">
-        <v>43002.96221257856</v>
+        <v>41731.10116290394</v>
       </c>
       <c r="D4" t="n">
-        <v>43002.96221257856</v>
+        <v>41731.10116290394</v>
       </c>
       <c r="E4" t="n">
-        <v>39605.09612781979</v>
+        <v>39622.30272959336</v>
       </c>
       <c r="F4" t="n">
-        <v>39605.09612781979</v>
+        <v>39622.30272959336</v>
       </c>
       <c r="G4" t="n">
-        <v>39605.09612781979</v>
+        <v>39622.30272959336</v>
       </c>
       <c r="H4" t="n">
-        <v>39605.09612781979</v>
+        <v>39622.30272959336</v>
       </c>
       <c r="I4" t="n">
-        <v>39605.09612781979</v>
+        <v>39622.30272959336</v>
       </c>
       <c r="J4" t="n">
-        <v>39605.09612781979</v>
+        <v>39622.30272959336</v>
       </c>
       <c r="K4" t="n">
-        <v>39605.09612781979</v>
+        <v>39622.30272959336</v>
       </c>
       <c r="L4" t="n">
-        <v>39605.09612781979</v>
+        <v>39622.30272959336</v>
       </c>
       <c r="M4" t="n">
-        <v>39605.09612781979</v>
+        <v>39622.30272959336</v>
       </c>
       <c r="N4" t="n">
-        <v>39605.09612781979</v>
+        <v>39622.30272959336</v>
       </c>
       <c r="O4" t="n">
-        <v>39605.09612781979</v>
+        <v>39622.30272959336</v>
       </c>
       <c r="P4" t="n">
-        <v>39605.09612781979</v>
+        <v>39622.30272959336</v>
       </c>
     </row>
     <row r="5">
@@ -26426,40 +26426,40 @@
         <v>33627.6</v>
       </c>
       <c r="E5" t="n">
-        <v>762.999999999999</v>
+        <v>501.6917425720072</v>
       </c>
       <c r="F5" t="n">
-        <v>762.999999999999</v>
+        <v>501.6917425720072</v>
       </c>
       <c r="G5" t="n">
-        <v>762.999999999999</v>
+        <v>501.6917425720072</v>
       </c>
       <c r="H5" t="n">
-        <v>762.999999999999</v>
+        <v>501.6917425720072</v>
       </c>
       <c r="I5" t="n">
-        <v>762.999999999999</v>
+        <v>501.6917425720072</v>
       </c>
       <c r="J5" t="n">
-        <v>762.999999999999</v>
+        <v>501.6917425720072</v>
       </c>
       <c r="K5" t="n">
-        <v>762.999999999999</v>
+        <v>501.6917425720072</v>
       </c>
       <c r="L5" t="n">
-        <v>762.999999999999</v>
+        <v>501.6917425720072</v>
       </c>
       <c r="M5" t="n">
-        <v>762.999999999999</v>
+        <v>501.6917425720072</v>
       </c>
       <c r="N5" t="n">
-        <v>762.999999999999</v>
+        <v>501.6917425720072</v>
       </c>
       <c r="O5" t="n">
-        <v>762.999999999999</v>
+        <v>501.6917425720072</v>
       </c>
       <c r="P5" t="n">
-        <v>762.999999999999</v>
+        <v>501.6917425720072</v>
       </c>
     </row>
     <row r="6">
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-17501.48917028304</v>
+        <v>-16229.62812060842</v>
       </c>
       <c r="C6" t="n">
-        <v>-17501.48917028304</v>
+        <v>-16229.62812060842</v>
       </c>
       <c r="D6" t="n">
-        <v>-17501.48917028304</v>
+        <v>-16229.62812060842</v>
       </c>
       <c r="E6" t="n">
-        <v>-8149.45401764132</v>
+        <v>1394.822258947179</v>
       </c>
       <c r="F6" t="n">
-        <v>19969.65098235864</v>
+        <v>19883.8429496618</v>
       </c>
       <c r="G6" t="n">
-        <v>19969.65098235864</v>
+        <v>19883.8429496618</v>
       </c>
       <c r="H6" t="n">
-        <v>19969.65098235864</v>
+        <v>19883.8429496618</v>
       </c>
       <c r="I6" t="n">
-        <v>19969.65098235865</v>
+        <v>19883.8429496618</v>
       </c>
       <c r="J6" t="n">
-        <v>19969.65098235865</v>
+        <v>19883.8429496618</v>
       </c>
       <c r="K6" t="n">
-        <v>19969.65098235864</v>
+        <v>19883.84294966181</v>
       </c>
       <c r="L6" t="n">
-        <v>19969.65098235864</v>
+        <v>19883.84294966179</v>
       </c>
       <c r="M6" t="n">
-        <v>19969.65098235863</v>
+        <v>19883.84294966179</v>
       </c>
       <c r="N6" t="n">
-        <v>19969.65098235864</v>
+        <v>19883.84294966179</v>
       </c>
       <c r="O6" t="n">
-        <v>19969.65098235865</v>
+        <v>19883.84294966179</v>
       </c>
       <c r="P6" t="n">
-        <v>19969.65098235865</v>
+        <v>19883.84294966179</v>
       </c>
     </row>
   </sheetData>
@@ -26684,40 +26684,40 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>34.99999999999995</v>
+        <v>23.01338268678932</v>
       </c>
       <c r="F3" t="n">
-        <v>34.99999999999995</v>
+        <v>23.01338268678932</v>
       </c>
       <c r="G3" t="n">
-        <v>34.99999999999995</v>
+        <v>23.01338268678932</v>
       </c>
       <c r="H3" t="n">
-        <v>34.99999999999995</v>
+        <v>23.01338268678932</v>
       </c>
       <c r="I3" t="n">
-        <v>34.99999999999995</v>
+        <v>23.01338268678932</v>
       </c>
       <c r="J3" t="n">
-        <v>34.99999999999995</v>
+        <v>23.01338268678932</v>
       </c>
       <c r="K3" t="n">
-        <v>34.99999999999995</v>
+        <v>23.01338268678932</v>
       </c>
       <c r="L3" t="n">
-        <v>34.99999999999995</v>
+        <v>23.01338268678932</v>
       </c>
       <c r="M3" t="n">
-        <v>34.99999999999995</v>
+        <v>23.01338268678932</v>
       </c>
       <c r="N3" t="n">
-        <v>34.99999999999995</v>
+        <v>23.01338268678932</v>
       </c>
       <c r="O3" t="n">
-        <v>34.99999999999995</v>
+        <v>23.01338268678932</v>
       </c>
       <c r="P3" t="n">
-        <v>34.99999999999995</v>
+        <v>23.01338268678932</v>
       </c>
     </row>
     <row r="4">
@@ -26840,49 +26840,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26892,49 +26892,49 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>35</v>
+        <v>23.01338268678932</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26947,46 +26947,46 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -31670,49 +31670,49 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1407035175879394</v>
+        <v>0.0925161113036756</v>
       </c>
       <c r="H11" t="n">
-        <v>1.440979899497485</v>
+        <v>0.9474806248887678</v>
       </c>
       <c r="I11" t="n">
-        <v>5.424472361809038</v>
+        <v>3.566727381034957</v>
       </c>
       <c r="J11" t="n">
-        <v>11.94203517587938</v>
+        <v>7.852189301760343</v>
       </c>
       <c r="K11" t="n">
-        <v>17.89801507537686</v>
+        <v>11.76839629324493</v>
       </c>
       <c r="L11" t="n">
-        <v>22.20407035175877</v>
+        <v>14.5997362345548</v>
       </c>
       <c r="M11" t="n">
-        <v>24.70630653266328</v>
+        <v>16.24501962895154</v>
       </c>
       <c r="N11" t="n">
-        <v>25.10608040201002</v>
+        <v>16.50788103019311</v>
       </c>
       <c r="O11" t="n">
-        <v>23.70695979899494</v>
+        <v>15.58792394841718</v>
       </c>
       <c r="P11" t="n">
-        <v>20.23334170854269</v>
+        <v>13.30393245060769</v>
       </c>
       <c r="Q11" t="n">
-        <v>15.1943969849246</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R11" t="n">
-        <v>8.838467336683406</v>
+        <v>5.811515176679517</v>
       </c>
       <c r="S11" t="n">
-        <v>3.206281407035172</v>
+        <v>2.10821088633251</v>
       </c>
       <c r="T11" t="n">
-        <v>0.615929648241205</v>
+        <v>0.4049892772318401</v>
       </c>
       <c r="U11" t="n">
-        <v>0.01125628140703515</v>
+        <v>0.007401288904294046</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -31749,49 +31749,49 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.07528301886792442</v>
+        <v>0.04950048351498081</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7270754716981123</v>
+        <v>0.4780704592104726</v>
       </c>
       <c r="I12" t="n">
-        <v>2.591981132075468</v>
+        <v>1.704292963125436</v>
       </c>
       <c r="J12" t="n">
-        <v>7.112594339622633</v>
+        <v>4.676710155246498</v>
       </c>
       <c r="K12" t="n">
-        <v>12.15655660377357</v>
+        <v>7.993242550750212</v>
       </c>
       <c r="L12" t="n">
-        <v>16.34599056603771</v>
+        <v>10.74790103688213</v>
       </c>
       <c r="M12" t="n">
-        <v>19.07499999999997</v>
+        <v>12.54229356430018</v>
       </c>
       <c r="N12" t="n">
-        <v>19.57985849056601</v>
+        <v>12.87425075418792</v>
       </c>
       <c r="O12" t="n">
-        <v>17.91174528301884</v>
+        <v>11.77742425104019</v>
       </c>
       <c r="P12" t="n">
-        <v>14.37575471698111</v>
+        <v>9.452421277522959</v>
       </c>
       <c r="Q12" t="n">
-        <v>9.609811320754705</v>
+        <v>6.318693299210532</v>
       </c>
       <c r="R12" t="n">
-        <v>4.674150943396222</v>
+        <v>3.073372125605564</v>
       </c>
       <c r="S12" t="n">
-        <v>1.398349056603771</v>
+        <v>0.9194497705523841</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3034433962264145</v>
+        <v>0.1995216857467866</v>
       </c>
       <c r="U12" t="n">
-        <v>0.004952830188679241</v>
+        <v>0.003256610757564528</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -31828,49 +31828,49 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.06311475409836056</v>
+        <v>0.04149954254994795</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5611475409836061</v>
+        <v>0.3689686601259011</v>
       </c>
       <c r="I13" t="n">
-        <v>1.898032786885244</v>
+        <v>1.248004425047526</v>
       </c>
       <c r="J13" t="n">
-        <v>4.462213114754091</v>
+        <v>2.93401765828132</v>
       </c>
       <c r="K13" t="n">
-        <v>7.332786885245889</v>
+        <v>4.821492307166679</v>
       </c>
       <c r="L13" t="n">
-        <v>9.383442622950806</v>
+        <v>6.169850171471354</v>
       </c>
       <c r="M13" t="n">
-        <v>9.893524590163919</v>
+        <v>6.505241928988658</v>
       </c>
       <c r="N13" t="n">
-        <v>9.658278688524582</v>
+        <v>6.350561815847948</v>
       </c>
       <c r="O13" t="n">
-        <v>8.920983606557368</v>
+        <v>5.865771705150827</v>
       </c>
       <c r="P13" t="n">
-        <v>7.633442622950805</v>
+        <v>5.019181037131885</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.284999999999992</v>
+        <v>3.475020785705187</v>
       </c>
       <c r="R13" t="n">
-        <v>2.837868852459011</v>
+        <v>1.865970340473114</v>
       </c>
       <c r="S13" t="n">
-        <v>1.099918032786883</v>
+        <v>0.7232238460750018</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2696721311475405</v>
+        <v>0.1773162272588685</v>
       </c>
       <c r="U13" t="n">
-        <v>0.003442622950819671</v>
+        <v>0.002263611411815345</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -31907,49 +31907,49 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1407035175879394</v>
+        <v>0.0925161113036756</v>
       </c>
       <c r="H14" t="n">
-        <v>1.440979899497485</v>
+        <v>0.9474806248887678</v>
       </c>
       <c r="I14" t="n">
-        <v>5.424472361809038</v>
+        <v>3.566727381034957</v>
       </c>
       <c r="J14" t="n">
-        <v>11.94203517587938</v>
+        <v>7.852189301760343</v>
       </c>
       <c r="K14" t="n">
-        <v>17.89801507537686</v>
+        <v>11.76839629324493</v>
       </c>
       <c r="L14" t="n">
-        <v>22.20407035175877</v>
+        <v>14.5997362345548</v>
       </c>
       <c r="M14" t="n">
-        <v>24.70630653266328</v>
+        <v>16.24501962895154</v>
       </c>
       <c r="N14" t="n">
-        <v>25.10608040201002</v>
+        <v>16.50788103019311</v>
       </c>
       <c r="O14" t="n">
-        <v>23.70695979899494</v>
+        <v>15.58792394841718</v>
       </c>
       <c r="P14" t="n">
-        <v>20.23334170854269</v>
+        <v>13.30393245060769</v>
       </c>
       <c r="Q14" t="n">
-        <v>15.1943969849246</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R14" t="n">
-        <v>8.838467336683406</v>
+        <v>5.811515176679517</v>
       </c>
       <c r="S14" t="n">
-        <v>3.206281407035172</v>
+        <v>2.10821088633251</v>
       </c>
       <c r="T14" t="n">
-        <v>0.615929648241205</v>
+        <v>0.4049892772318401</v>
       </c>
       <c r="U14" t="n">
-        <v>0.01125628140703515</v>
+        <v>0.007401288904294046</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -31986,49 +31986,49 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.07528301886792442</v>
+        <v>0.04950048351498081</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7270754716981123</v>
+        <v>0.4780704592104726</v>
       </c>
       <c r="I15" t="n">
-        <v>2.591981132075468</v>
+        <v>1.704292963125436</v>
       </c>
       <c r="J15" t="n">
-        <v>7.112594339622633</v>
+        <v>4.676710155246498</v>
       </c>
       <c r="K15" t="n">
-        <v>12.15655660377357</v>
+        <v>7.993242550750212</v>
       </c>
       <c r="L15" t="n">
-        <v>16.34599056603771</v>
+        <v>10.74790103688213</v>
       </c>
       <c r="M15" t="n">
-        <v>19.07499999999997</v>
+        <v>12.54229356430018</v>
       </c>
       <c r="N15" t="n">
-        <v>19.57985849056601</v>
+        <v>12.87425075418792</v>
       </c>
       <c r="O15" t="n">
-        <v>17.91174528301884</v>
+        <v>11.77742425104019</v>
       </c>
       <c r="P15" t="n">
-        <v>14.37575471698111</v>
+        <v>9.452421277522959</v>
       </c>
       <c r="Q15" t="n">
-        <v>9.609811320754705</v>
+        <v>6.318693299210532</v>
       </c>
       <c r="R15" t="n">
-        <v>4.674150943396222</v>
+        <v>3.073372125605564</v>
       </c>
       <c r="S15" t="n">
-        <v>1.398349056603771</v>
+        <v>0.9194497705523841</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3034433962264145</v>
+        <v>0.1995216857467866</v>
       </c>
       <c r="U15" t="n">
-        <v>0.004952830188679241</v>
+        <v>0.003256610757564528</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -32065,49 +32065,49 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.06311475409836056</v>
+        <v>0.04149954254994795</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5611475409836061</v>
+        <v>0.3689686601259011</v>
       </c>
       <c r="I16" t="n">
-        <v>1.898032786885244</v>
+        <v>1.248004425047526</v>
       </c>
       <c r="J16" t="n">
-        <v>4.462213114754091</v>
+        <v>2.93401765828132</v>
       </c>
       <c r="K16" t="n">
-        <v>7.332786885245889</v>
+        <v>4.821492307166679</v>
       </c>
       <c r="L16" t="n">
-        <v>9.383442622950806</v>
+        <v>6.169850171471354</v>
       </c>
       <c r="M16" t="n">
-        <v>9.893524590163919</v>
+        <v>6.505241928988658</v>
       </c>
       <c r="N16" t="n">
-        <v>9.658278688524582</v>
+        <v>6.350561815847948</v>
       </c>
       <c r="O16" t="n">
-        <v>8.920983606557368</v>
+        <v>5.865771705150827</v>
       </c>
       <c r="P16" t="n">
-        <v>7.633442622950805</v>
+        <v>5.019181037131885</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.284999999999992</v>
+        <v>3.475020785705187</v>
       </c>
       <c r="R16" t="n">
-        <v>2.837868852459011</v>
+        <v>1.865970340473114</v>
       </c>
       <c r="S16" t="n">
-        <v>1.099918032786883</v>
+        <v>0.7232238460750018</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2696721311475405</v>
+        <v>0.1773162272588685</v>
       </c>
       <c r="U16" t="n">
-        <v>0.003442622950819671</v>
+        <v>0.002263611411815345</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -32144,49 +32144,49 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1407035175879394</v>
+        <v>0.0925161113036756</v>
       </c>
       <c r="H17" t="n">
-        <v>1.440979899497485</v>
+        <v>0.9474806248887678</v>
       </c>
       <c r="I17" t="n">
-        <v>5.424472361809038</v>
+        <v>3.566727381034957</v>
       </c>
       <c r="J17" t="n">
-        <v>11.94203517587938</v>
+        <v>7.852189301760343</v>
       </c>
       <c r="K17" t="n">
-        <v>17.89801507537686</v>
+        <v>11.76839629324493</v>
       </c>
       <c r="L17" t="n">
-        <v>22.20407035175877</v>
+        <v>14.5997362345548</v>
       </c>
       <c r="M17" t="n">
-        <v>24.70630653266328</v>
+        <v>16.24501962895154</v>
       </c>
       <c r="N17" t="n">
-        <v>25.10608040201002</v>
+        <v>16.50788103019311</v>
       </c>
       <c r="O17" t="n">
-        <v>23.70695979899494</v>
+        <v>15.58792394841718</v>
       </c>
       <c r="P17" t="n">
-        <v>20.23334170854269</v>
+        <v>13.30393245060769</v>
       </c>
       <c r="Q17" t="n">
-        <v>15.1943969849246</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R17" t="n">
-        <v>8.838467336683406</v>
+        <v>5.811515176679517</v>
       </c>
       <c r="S17" t="n">
-        <v>3.206281407035172</v>
+        <v>2.10821088633251</v>
       </c>
       <c r="T17" t="n">
-        <v>0.615929648241205</v>
+        <v>0.4049892772318401</v>
       </c>
       <c r="U17" t="n">
-        <v>0.01125628140703515</v>
+        <v>0.007401288904294046</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -32223,49 +32223,49 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.07528301886792442</v>
+        <v>0.04950048351498081</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7270754716981123</v>
+        <v>0.4780704592104726</v>
       </c>
       <c r="I18" t="n">
-        <v>2.591981132075468</v>
+        <v>1.704292963125436</v>
       </c>
       <c r="J18" t="n">
-        <v>7.112594339622633</v>
+        <v>4.676710155246498</v>
       </c>
       <c r="K18" t="n">
-        <v>12.15655660377357</v>
+        <v>7.993242550750212</v>
       </c>
       <c r="L18" t="n">
-        <v>16.34599056603771</v>
+        <v>10.74790103688213</v>
       </c>
       <c r="M18" t="n">
-        <v>19.07499999999997</v>
+        <v>12.54229356430018</v>
       </c>
       <c r="N18" t="n">
-        <v>19.57985849056601</v>
+        <v>12.87425075418792</v>
       </c>
       <c r="O18" t="n">
-        <v>17.91174528301884</v>
+        <v>11.77742425104019</v>
       </c>
       <c r="P18" t="n">
-        <v>14.37575471698111</v>
+        <v>9.452421277522959</v>
       </c>
       <c r="Q18" t="n">
-        <v>9.609811320754705</v>
+        <v>6.318693299210532</v>
       </c>
       <c r="R18" t="n">
-        <v>4.674150943396222</v>
+        <v>3.073372125605564</v>
       </c>
       <c r="S18" t="n">
-        <v>1.398349056603771</v>
+        <v>0.9194497705523841</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3034433962264145</v>
+        <v>0.1995216857467866</v>
       </c>
       <c r="U18" t="n">
-        <v>0.004952830188679241</v>
+        <v>0.003256610757564528</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -32302,49 +32302,49 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.06311475409836056</v>
+        <v>0.04149954254994795</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5611475409836061</v>
+        <v>0.3689686601259011</v>
       </c>
       <c r="I19" t="n">
-        <v>1.898032786885244</v>
+        <v>1.248004425047526</v>
       </c>
       <c r="J19" t="n">
-        <v>4.462213114754091</v>
+        <v>2.93401765828132</v>
       </c>
       <c r="K19" t="n">
-        <v>7.332786885245889</v>
+        <v>4.821492307166679</v>
       </c>
       <c r="L19" t="n">
-        <v>9.383442622950806</v>
+        <v>6.169850171471354</v>
       </c>
       <c r="M19" t="n">
-        <v>9.893524590163919</v>
+        <v>6.505241928988658</v>
       </c>
       <c r="N19" t="n">
-        <v>9.658278688524582</v>
+        <v>6.350561815847948</v>
       </c>
       <c r="O19" t="n">
-        <v>8.920983606557368</v>
+        <v>5.865771705150827</v>
       </c>
       <c r="P19" t="n">
-        <v>7.633442622950805</v>
+        <v>5.019181037131885</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.284999999999992</v>
+        <v>3.475020785705187</v>
       </c>
       <c r="R19" t="n">
-        <v>2.837868852459011</v>
+        <v>1.865970340473114</v>
       </c>
       <c r="S19" t="n">
-        <v>1.099918032786883</v>
+        <v>0.7232238460750018</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2696721311475405</v>
+        <v>0.1773162272588685</v>
       </c>
       <c r="U19" t="n">
-        <v>0.003442622950819671</v>
+        <v>0.002263611411815345</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -32381,49 +32381,49 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1407035175879394</v>
+        <v>0.0925161113036756</v>
       </c>
       <c r="H20" t="n">
-        <v>1.440979899497485</v>
+        <v>0.9474806248887678</v>
       </c>
       <c r="I20" t="n">
-        <v>5.424472361809038</v>
+        <v>3.566727381034957</v>
       </c>
       <c r="J20" t="n">
-        <v>11.94203517587938</v>
+        <v>7.852189301760343</v>
       </c>
       <c r="K20" t="n">
-        <v>17.89801507537686</v>
+        <v>11.76839629324493</v>
       </c>
       <c r="L20" t="n">
-        <v>22.20407035175877</v>
+        <v>14.5997362345548</v>
       </c>
       <c r="M20" t="n">
-        <v>24.70630653266328</v>
+        <v>16.24501962895154</v>
       </c>
       <c r="N20" t="n">
-        <v>25.10608040201002</v>
+        <v>16.50788103019311</v>
       </c>
       <c r="O20" t="n">
-        <v>23.70695979899494</v>
+        <v>15.58792394841718</v>
       </c>
       <c r="P20" t="n">
-        <v>20.23334170854269</v>
+        <v>13.30393245060769</v>
       </c>
       <c r="Q20" t="n">
-        <v>15.1943969849246</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R20" t="n">
-        <v>8.838467336683406</v>
+        <v>5.811515176679517</v>
       </c>
       <c r="S20" t="n">
-        <v>3.206281407035172</v>
+        <v>2.10821088633251</v>
       </c>
       <c r="T20" t="n">
-        <v>0.615929648241205</v>
+        <v>0.4049892772318401</v>
       </c>
       <c r="U20" t="n">
-        <v>0.01125628140703515</v>
+        <v>0.007401288904294046</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -32460,49 +32460,49 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.07528301886792442</v>
+        <v>0.04950048351498081</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7270754716981123</v>
+        <v>0.4780704592104726</v>
       </c>
       <c r="I21" t="n">
-        <v>2.591981132075468</v>
+        <v>1.704292963125436</v>
       </c>
       <c r="J21" t="n">
-        <v>7.112594339622633</v>
+        <v>4.676710155246498</v>
       </c>
       <c r="K21" t="n">
-        <v>12.15655660377357</v>
+        <v>7.993242550750212</v>
       </c>
       <c r="L21" t="n">
-        <v>16.34599056603771</v>
+        <v>10.74790103688213</v>
       </c>
       <c r="M21" t="n">
-        <v>19.07499999999997</v>
+        <v>12.54229356430018</v>
       </c>
       <c r="N21" t="n">
-        <v>19.57985849056601</v>
+        <v>12.87425075418792</v>
       </c>
       <c r="O21" t="n">
-        <v>17.91174528301884</v>
+        <v>11.77742425104019</v>
       </c>
       <c r="P21" t="n">
-        <v>14.37575471698111</v>
+        <v>9.452421277522959</v>
       </c>
       <c r="Q21" t="n">
-        <v>9.609811320754705</v>
+        <v>6.318693299210532</v>
       </c>
       <c r="R21" t="n">
-        <v>4.674150943396222</v>
+        <v>3.073372125605564</v>
       </c>
       <c r="S21" t="n">
-        <v>1.398349056603771</v>
+        <v>0.9194497705523841</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3034433962264145</v>
+        <v>0.1995216857467866</v>
       </c>
       <c r="U21" t="n">
-        <v>0.004952830188679241</v>
+        <v>0.003256610757564528</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -32539,49 +32539,49 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.06311475409836056</v>
+        <v>0.04149954254994795</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5611475409836061</v>
+        <v>0.3689686601259011</v>
       </c>
       <c r="I22" t="n">
-        <v>1.898032786885244</v>
+        <v>1.248004425047526</v>
       </c>
       <c r="J22" t="n">
-        <v>4.462213114754091</v>
+        <v>2.93401765828132</v>
       </c>
       <c r="K22" t="n">
-        <v>7.332786885245889</v>
+        <v>4.821492307166679</v>
       </c>
       <c r="L22" t="n">
-        <v>9.383442622950806</v>
+        <v>6.169850171471354</v>
       </c>
       <c r="M22" t="n">
-        <v>9.893524590163919</v>
+        <v>6.505241928988658</v>
       </c>
       <c r="N22" t="n">
-        <v>9.658278688524582</v>
+        <v>6.350561815847948</v>
       </c>
       <c r="O22" t="n">
-        <v>8.920983606557368</v>
+        <v>5.865771705150827</v>
       </c>
       <c r="P22" t="n">
-        <v>7.633442622950805</v>
+        <v>5.019181037131885</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.284999999999992</v>
+        <v>3.475020785705187</v>
       </c>
       <c r="R22" t="n">
-        <v>2.837868852459011</v>
+        <v>1.865970340473114</v>
       </c>
       <c r="S22" t="n">
-        <v>1.099918032786883</v>
+        <v>0.7232238460750018</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2696721311475405</v>
+        <v>0.1773162272588685</v>
       </c>
       <c r="U22" t="n">
-        <v>0.003442622950819671</v>
+        <v>0.002263611411815345</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -32618,49 +32618,49 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1407035175879394</v>
+        <v>0.0925161113036756</v>
       </c>
       <c r="H23" t="n">
-        <v>1.440979899497485</v>
+        <v>0.9474806248887678</v>
       </c>
       <c r="I23" t="n">
-        <v>5.424472361809038</v>
+        <v>3.566727381034957</v>
       </c>
       <c r="J23" t="n">
-        <v>11.94203517587938</v>
+        <v>7.852189301760343</v>
       </c>
       <c r="K23" t="n">
-        <v>17.89801507537686</v>
+        <v>11.76839629324493</v>
       </c>
       <c r="L23" t="n">
-        <v>22.20407035175877</v>
+        <v>14.5997362345548</v>
       </c>
       <c r="M23" t="n">
-        <v>24.70630653266328</v>
+        <v>16.24501962895154</v>
       </c>
       <c r="N23" t="n">
-        <v>25.10608040201002</v>
+        <v>16.50788103019311</v>
       </c>
       <c r="O23" t="n">
-        <v>23.70695979899494</v>
+        <v>15.58792394841718</v>
       </c>
       <c r="P23" t="n">
-        <v>20.23334170854269</v>
+        <v>13.30393245060769</v>
       </c>
       <c r="Q23" t="n">
-        <v>15.1943969849246</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R23" t="n">
-        <v>8.838467336683406</v>
+        <v>5.811515176679517</v>
       </c>
       <c r="S23" t="n">
-        <v>3.206281407035172</v>
+        <v>2.10821088633251</v>
       </c>
       <c r="T23" t="n">
-        <v>0.615929648241205</v>
+        <v>0.4049892772318401</v>
       </c>
       <c r="U23" t="n">
-        <v>0.01125628140703515</v>
+        <v>0.007401288904294046</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -32697,49 +32697,49 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.07528301886792442</v>
+        <v>0.04950048351498081</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7270754716981123</v>
+        <v>0.4780704592104726</v>
       </c>
       <c r="I24" t="n">
-        <v>2.591981132075468</v>
+        <v>1.704292963125436</v>
       </c>
       <c r="J24" t="n">
-        <v>7.112594339622633</v>
+        <v>4.676710155246498</v>
       </c>
       <c r="K24" t="n">
-        <v>12.15655660377357</v>
+        <v>7.993242550750212</v>
       </c>
       <c r="L24" t="n">
-        <v>16.34599056603771</v>
+        <v>10.74790103688213</v>
       </c>
       <c r="M24" t="n">
-        <v>19.07499999999997</v>
+        <v>12.54229356430018</v>
       </c>
       <c r="N24" t="n">
-        <v>19.57985849056601</v>
+        <v>12.87425075418792</v>
       </c>
       <c r="O24" t="n">
-        <v>17.91174528301884</v>
+        <v>11.77742425104019</v>
       </c>
       <c r="P24" t="n">
-        <v>14.37575471698111</v>
+        <v>9.452421277522959</v>
       </c>
       <c r="Q24" t="n">
-        <v>9.609811320754705</v>
+        <v>6.318693299210532</v>
       </c>
       <c r="R24" t="n">
-        <v>4.674150943396222</v>
+        <v>3.073372125605564</v>
       </c>
       <c r="S24" t="n">
-        <v>1.398349056603771</v>
+        <v>0.9194497705523841</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3034433962264145</v>
+        <v>0.1995216857467866</v>
       </c>
       <c r="U24" t="n">
-        <v>0.004952830188679241</v>
+        <v>0.003256610757564528</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -32776,49 +32776,49 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.06311475409836056</v>
+        <v>0.04149954254994795</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5611475409836061</v>
+        <v>0.3689686601259011</v>
       </c>
       <c r="I25" t="n">
-        <v>1.898032786885244</v>
+        <v>1.248004425047526</v>
       </c>
       <c r="J25" t="n">
-        <v>4.462213114754091</v>
+        <v>2.93401765828132</v>
       </c>
       <c r="K25" t="n">
-        <v>7.332786885245889</v>
+        <v>4.821492307166679</v>
       </c>
       <c r="L25" t="n">
-        <v>9.383442622950806</v>
+        <v>6.169850171471354</v>
       </c>
       <c r="M25" t="n">
-        <v>9.893524590163919</v>
+        <v>6.505241928988658</v>
       </c>
       <c r="N25" t="n">
-        <v>9.658278688524582</v>
+        <v>6.350561815847948</v>
       </c>
       <c r="O25" t="n">
-        <v>8.920983606557368</v>
+        <v>5.865771705150827</v>
       </c>
       <c r="P25" t="n">
-        <v>7.633442622950805</v>
+        <v>5.019181037131885</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.284999999999992</v>
+        <v>3.475020785705187</v>
       </c>
       <c r="R25" t="n">
-        <v>2.837868852459011</v>
+        <v>1.865970340473114</v>
       </c>
       <c r="S25" t="n">
-        <v>1.099918032786883</v>
+        <v>0.7232238460750018</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2696721311475405</v>
+        <v>0.1773162272588685</v>
       </c>
       <c r="U25" t="n">
-        <v>0.003442622950819671</v>
+        <v>0.002263611411815345</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -32855,49 +32855,49 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1407035175879394</v>
+        <v>0.0925161113036756</v>
       </c>
       <c r="H26" t="n">
-        <v>1.440979899497485</v>
+        <v>0.9474806248887678</v>
       </c>
       <c r="I26" t="n">
-        <v>5.424472361809038</v>
+        <v>3.566727381034957</v>
       </c>
       <c r="J26" t="n">
-        <v>11.94203517587938</v>
+        <v>7.852189301760343</v>
       </c>
       <c r="K26" t="n">
-        <v>17.89801507537686</v>
+        <v>11.76839629324493</v>
       </c>
       <c r="L26" t="n">
-        <v>22.20407035175877</v>
+        <v>14.5997362345548</v>
       </c>
       <c r="M26" t="n">
-        <v>24.70630653266328</v>
+        <v>16.24501962895154</v>
       </c>
       <c r="N26" t="n">
-        <v>25.10608040201002</v>
+        <v>16.50788103019311</v>
       </c>
       <c r="O26" t="n">
-        <v>23.70695979899494</v>
+        <v>15.58792394841718</v>
       </c>
       <c r="P26" t="n">
-        <v>20.23334170854269</v>
+        <v>13.30393245060769</v>
       </c>
       <c r="Q26" t="n">
-        <v>15.1943969849246</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R26" t="n">
-        <v>8.838467336683406</v>
+        <v>5.811515176679517</v>
       </c>
       <c r="S26" t="n">
-        <v>3.206281407035172</v>
+        <v>2.10821088633251</v>
       </c>
       <c r="T26" t="n">
-        <v>0.615929648241205</v>
+        <v>0.4049892772318401</v>
       </c>
       <c r="U26" t="n">
-        <v>0.01125628140703515</v>
+        <v>0.007401288904294046</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -32934,49 +32934,49 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.07528301886792442</v>
+        <v>0.04950048351498081</v>
       </c>
       <c r="H27" t="n">
-        <v>0.7270754716981123</v>
+        <v>0.4780704592104726</v>
       </c>
       <c r="I27" t="n">
-        <v>2.591981132075468</v>
+        <v>1.704292963125436</v>
       </c>
       <c r="J27" t="n">
-        <v>7.112594339622633</v>
+        <v>4.676710155246498</v>
       </c>
       <c r="K27" t="n">
-        <v>12.15655660377357</v>
+        <v>7.993242550750212</v>
       </c>
       <c r="L27" t="n">
-        <v>16.34599056603771</v>
+        <v>10.74790103688213</v>
       </c>
       <c r="M27" t="n">
-        <v>19.07499999999997</v>
+        <v>12.54229356430018</v>
       </c>
       <c r="N27" t="n">
-        <v>19.57985849056601</v>
+        <v>12.87425075418792</v>
       </c>
       <c r="O27" t="n">
-        <v>17.91174528301884</v>
+        <v>11.77742425104019</v>
       </c>
       <c r="P27" t="n">
-        <v>14.37575471698111</v>
+        <v>9.452421277522959</v>
       </c>
       <c r="Q27" t="n">
-        <v>9.609811320754705</v>
+        <v>6.318693299210532</v>
       </c>
       <c r="R27" t="n">
-        <v>4.674150943396222</v>
+        <v>3.073372125605564</v>
       </c>
       <c r="S27" t="n">
-        <v>1.398349056603771</v>
+        <v>0.9194497705523841</v>
       </c>
       <c r="T27" t="n">
-        <v>0.3034433962264145</v>
+        <v>0.1995216857467866</v>
       </c>
       <c r="U27" t="n">
-        <v>0.004952830188679241</v>
+        <v>0.003256610757564528</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -33013,49 +33013,49 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.06311475409836056</v>
+        <v>0.04149954254994795</v>
       </c>
       <c r="H28" t="n">
-        <v>0.5611475409836061</v>
+        <v>0.3689686601259011</v>
       </c>
       <c r="I28" t="n">
-        <v>1.898032786885244</v>
+        <v>1.248004425047526</v>
       </c>
       <c r="J28" t="n">
-        <v>4.462213114754091</v>
+        <v>2.93401765828132</v>
       </c>
       <c r="K28" t="n">
-        <v>7.332786885245889</v>
+        <v>4.821492307166679</v>
       </c>
       <c r="L28" t="n">
-        <v>9.383442622950806</v>
+        <v>6.169850171471354</v>
       </c>
       <c r="M28" t="n">
-        <v>9.893524590163919</v>
+        <v>6.505241928988658</v>
       </c>
       <c r="N28" t="n">
-        <v>9.658278688524582</v>
+        <v>6.350561815847948</v>
       </c>
       <c r="O28" t="n">
-        <v>8.920983606557368</v>
+        <v>5.865771705150827</v>
       </c>
       <c r="P28" t="n">
-        <v>7.633442622950805</v>
+        <v>5.019181037131885</v>
       </c>
       <c r="Q28" t="n">
-        <v>5.284999999999992</v>
+        <v>3.475020785705187</v>
       </c>
       <c r="R28" t="n">
-        <v>2.837868852459011</v>
+        <v>1.865970340473114</v>
       </c>
       <c r="S28" t="n">
-        <v>1.099918032786883</v>
+        <v>0.7232238460750018</v>
       </c>
       <c r="T28" t="n">
-        <v>0.2696721311475405</v>
+        <v>0.1773162272588685</v>
       </c>
       <c r="U28" t="n">
-        <v>0.003442622950819671</v>
+        <v>0.002263611411815345</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -33092,49 +33092,49 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1407035175879394</v>
+        <v>0.0925161113036756</v>
       </c>
       <c r="H29" t="n">
-        <v>1.440979899497485</v>
+        <v>0.9474806248887678</v>
       </c>
       <c r="I29" t="n">
-        <v>5.424472361809038</v>
+        <v>3.566727381034957</v>
       </c>
       <c r="J29" t="n">
-        <v>11.94203517587938</v>
+        <v>7.852189301760343</v>
       </c>
       <c r="K29" t="n">
-        <v>17.89801507537686</v>
+        <v>11.76839629324493</v>
       </c>
       <c r="L29" t="n">
-        <v>22.20407035175877</v>
+        <v>14.5997362345548</v>
       </c>
       <c r="M29" t="n">
-        <v>24.70630653266328</v>
+        <v>16.24501962895154</v>
       </c>
       <c r="N29" t="n">
-        <v>25.10608040201002</v>
+        <v>16.50788103019311</v>
       </c>
       <c r="O29" t="n">
-        <v>23.70695979899494</v>
+        <v>15.58792394841718</v>
       </c>
       <c r="P29" t="n">
-        <v>20.23334170854269</v>
+        <v>13.30393245060769</v>
       </c>
       <c r="Q29" t="n">
-        <v>15.1943969849246</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R29" t="n">
-        <v>8.838467336683406</v>
+        <v>5.811515176679517</v>
       </c>
       <c r="S29" t="n">
-        <v>3.206281407035172</v>
+        <v>2.10821088633251</v>
       </c>
       <c r="T29" t="n">
-        <v>0.615929648241205</v>
+        <v>0.4049892772318401</v>
       </c>
       <c r="U29" t="n">
-        <v>0.01125628140703515</v>
+        <v>0.007401288904294046</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -33171,49 +33171,49 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.07528301886792442</v>
+        <v>0.04950048351498081</v>
       </c>
       <c r="H30" t="n">
-        <v>0.7270754716981123</v>
+        <v>0.4780704592104726</v>
       </c>
       <c r="I30" t="n">
-        <v>2.591981132075468</v>
+        <v>1.704292963125436</v>
       </c>
       <c r="J30" t="n">
-        <v>7.112594339622633</v>
+        <v>4.676710155246498</v>
       </c>
       <c r="K30" t="n">
-        <v>12.15655660377357</v>
+        <v>7.993242550750212</v>
       </c>
       <c r="L30" t="n">
-        <v>16.34599056603771</v>
+        <v>10.74790103688213</v>
       </c>
       <c r="M30" t="n">
-        <v>19.07499999999997</v>
+        <v>12.54229356430018</v>
       </c>
       <c r="N30" t="n">
-        <v>19.57985849056601</v>
+        <v>12.87425075418792</v>
       </c>
       <c r="O30" t="n">
-        <v>17.91174528301884</v>
+        <v>11.77742425104019</v>
       </c>
       <c r="P30" t="n">
-        <v>14.37575471698111</v>
+        <v>9.452421277522959</v>
       </c>
       <c r="Q30" t="n">
-        <v>9.609811320754705</v>
+        <v>6.318693299210532</v>
       </c>
       <c r="R30" t="n">
-        <v>4.674150943396222</v>
+        <v>3.073372125605564</v>
       </c>
       <c r="S30" t="n">
-        <v>1.398349056603771</v>
+        <v>0.9194497705523841</v>
       </c>
       <c r="T30" t="n">
-        <v>0.3034433962264145</v>
+        <v>0.1995216857467866</v>
       </c>
       <c r="U30" t="n">
-        <v>0.004952830188679241</v>
+        <v>0.003256610757564528</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -33250,49 +33250,49 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.06311475409836056</v>
+        <v>0.04149954254994795</v>
       </c>
       <c r="H31" t="n">
-        <v>0.5611475409836061</v>
+        <v>0.3689686601259011</v>
       </c>
       <c r="I31" t="n">
-        <v>1.898032786885244</v>
+        <v>1.248004425047526</v>
       </c>
       <c r="J31" t="n">
-        <v>4.462213114754091</v>
+        <v>2.93401765828132</v>
       </c>
       <c r="K31" t="n">
-        <v>7.332786885245889</v>
+        <v>4.821492307166679</v>
       </c>
       <c r="L31" t="n">
-        <v>9.383442622950806</v>
+        <v>6.169850171471354</v>
       </c>
       <c r="M31" t="n">
-        <v>9.893524590163919</v>
+        <v>6.505241928988658</v>
       </c>
       <c r="N31" t="n">
-        <v>9.658278688524582</v>
+        <v>6.350561815847948</v>
       </c>
       <c r="O31" t="n">
-        <v>8.920983606557368</v>
+        <v>5.865771705150827</v>
       </c>
       <c r="P31" t="n">
-        <v>7.633442622950805</v>
+        <v>5.019181037131885</v>
       </c>
       <c r="Q31" t="n">
-        <v>5.284999999999992</v>
+        <v>3.475020785705187</v>
       </c>
       <c r="R31" t="n">
-        <v>2.837868852459011</v>
+        <v>1.865970340473114</v>
       </c>
       <c r="S31" t="n">
-        <v>1.099918032786883</v>
+        <v>0.7232238460750018</v>
       </c>
       <c r="T31" t="n">
-        <v>0.2696721311475405</v>
+        <v>0.1773162272588685</v>
       </c>
       <c r="U31" t="n">
-        <v>0.003442622950819671</v>
+        <v>0.002263611411815345</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -33329,49 +33329,49 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.1407035175879394</v>
+        <v>0.09251611130367558</v>
       </c>
       <c r="H32" t="n">
-        <v>1.440979899497485</v>
+        <v>0.9474806248887679</v>
       </c>
       <c r="I32" t="n">
-        <v>5.424472361809038</v>
+        <v>3.566727381034957</v>
       </c>
       <c r="J32" t="n">
-        <v>11.94203517587938</v>
+        <v>7.852189301760344</v>
       </c>
       <c r="K32" t="n">
-        <v>17.89801507537686</v>
+        <v>11.76839629324494</v>
       </c>
       <c r="L32" t="n">
-        <v>22.20407035175877</v>
+        <v>14.5997362345548</v>
       </c>
       <c r="M32" t="n">
-        <v>24.70630653266328</v>
+        <v>16.24501962895154</v>
       </c>
       <c r="N32" t="n">
-        <v>25.10608040201002</v>
+        <v>16.50788103019311</v>
       </c>
       <c r="O32" t="n">
-        <v>23.70695979899494</v>
+        <v>15.58792394841718</v>
       </c>
       <c r="P32" t="n">
-        <v>20.23334170854269</v>
+        <v>13.30393245060769</v>
       </c>
       <c r="Q32" t="n">
-        <v>15.1943969849246</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R32" t="n">
-        <v>8.838467336683406</v>
+        <v>5.811515176679516</v>
       </c>
       <c r="S32" t="n">
-        <v>3.206281407035172</v>
+        <v>2.108210886332509</v>
       </c>
       <c r="T32" t="n">
-        <v>0.615929648241205</v>
+        <v>0.4049892772318401</v>
       </c>
       <c r="U32" t="n">
-        <v>0.01125628140703515</v>
+        <v>0.007401288904294046</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -33408,49 +33408,49 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.07528301886792442</v>
+        <v>0.0495004835149808</v>
       </c>
       <c r="H33" t="n">
-        <v>0.7270754716981123</v>
+        <v>0.4780704592104726</v>
       </c>
       <c r="I33" t="n">
-        <v>2.591981132075468</v>
+        <v>1.704292963125436</v>
       </c>
       <c r="J33" t="n">
-        <v>7.112594339622633</v>
+        <v>4.676710155246499</v>
       </c>
       <c r="K33" t="n">
-        <v>12.15655660377357</v>
+        <v>7.993242550750212</v>
       </c>
       <c r="L33" t="n">
-        <v>16.34599056603771</v>
+        <v>10.74790103688213</v>
       </c>
       <c r="M33" t="n">
-        <v>19.07499999999997</v>
+        <v>12.54229356430018</v>
       </c>
       <c r="N33" t="n">
-        <v>19.57985849056601</v>
+        <v>12.87425075418792</v>
       </c>
       <c r="O33" t="n">
-        <v>17.91174528301884</v>
+        <v>11.77742425104019</v>
       </c>
       <c r="P33" t="n">
-        <v>14.37575471698111</v>
+        <v>9.452421277522957</v>
       </c>
       <c r="Q33" t="n">
-        <v>9.609811320754705</v>
+        <v>6.318693299210532</v>
       </c>
       <c r="R33" t="n">
-        <v>4.674150943396222</v>
+        <v>3.073372125605564</v>
       </c>
       <c r="S33" t="n">
-        <v>1.398349056603771</v>
+        <v>0.9194497705523841</v>
       </c>
       <c r="T33" t="n">
-        <v>0.3034433962264145</v>
+        <v>0.1995216857467866</v>
       </c>
       <c r="U33" t="n">
-        <v>0.004952830188679241</v>
+        <v>0.003256610757564528</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -33487,49 +33487,49 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.06311475409836056</v>
+        <v>0.04149954254994795</v>
       </c>
       <c r="H34" t="n">
-        <v>0.5611475409836061</v>
+        <v>0.3689686601259011</v>
       </c>
       <c r="I34" t="n">
-        <v>1.898032786885244</v>
+        <v>1.248004425047526</v>
       </c>
       <c r="J34" t="n">
-        <v>4.462213114754091</v>
+        <v>2.93401765828132</v>
       </c>
       <c r="K34" t="n">
-        <v>7.332786885245889</v>
+        <v>4.821492307166679</v>
       </c>
       <c r="L34" t="n">
-        <v>9.383442622950806</v>
+        <v>6.169850171471354</v>
       </c>
       <c r="M34" t="n">
-        <v>9.893524590163919</v>
+        <v>6.505241928988658</v>
       </c>
       <c r="N34" t="n">
-        <v>9.658278688524582</v>
+        <v>6.350561815847949</v>
       </c>
       <c r="O34" t="n">
-        <v>8.920983606557368</v>
+        <v>5.865771705150827</v>
       </c>
       <c r="P34" t="n">
-        <v>7.633442622950805</v>
+        <v>5.019181037131885</v>
       </c>
       <c r="Q34" t="n">
-        <v>5.284999999999992</v>
+        <v>3.475020785705187</v>
       </c>
       <c r="R34" t="n">
-        <v>2.837868852459011</v>
+        <v>1.865970340473114</v>
       </c>
       <c r="S34" t="n">
-        <v>1.099918032786883</v>
+        <v>0.7232238460750018</v>
       </c>
       <c r="T34" t="n">
-        <v>0.2696721311475405</v>
+        <v>0.1773162272588684</v>
       </c>
       <c r="U34" t="n">
-        <v>0.003442622950819671</v>
+        <v>0.002263611411815345</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -33566,49 +33566,49 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0.1407035175879394</v>
+        <v>0.0925161113036756</v>
       </c>
       <c r="H35" t="n">
-        <v>1.440979899497485</v>
+        <v>0.9474806248887678</v>
       </c>
       <c r="I35" t="n">
-        <v>5.424472361809038</v>
+        <v>3.566727381034957</v>
       </c>
       <c r="J35" t="n">
-        <v>11.94203517587938</v>
+        <v>7.852189301760343</v>
       </c>
       <c r="K35" t="n">
-        <v>17.89801507537686</v>
+        <v>11.76839629324493</v>
       </c>
       <c r="L35" t="n">
-        <v>22.20407035175877</v>
+        <v>14.5997362345548</v>
       </c>
       <c r="M35" t="n">
-        <v>24.70630653266328</v>
+        <v>16.24501962895154</v>
       </c>
       <c r="N35" t="n">
-        <v>25.10608040201002</v>
+        <v>16.50788103019311</v>
       </c>
       <c r="O35" t="n">
-        <v>23.70695979899494</v>
+        <v>15.58792394841718</v>
       </c>
       <c r="P35" t="n">
-        <v>20.23334170854269</v>
+        <v>13.30393245060769</v>
       </c>
       <c r="Q35" t="n">
-        <v>15.1943969849246</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R35" t="n">
-        <v>8.838467336683406</v>
+        <v>5.811515176679517</v>
       </c>
       <c r="S35" t="n">
-        <v>3.206281407035172</v>
+        <v>2.10821088633251</v>
       </c>
       <c r="T35" t="n">
-        <v>0.615929648241205</v>
+        <v>0.4049892772318401</v>
       </c>
       <c r="U35" t="n">
-        <v>0.01125628140703515</v>
+        <v>0.007401288904294046</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -33645,49 +33645,49 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0.07528301886792442</v>
+        <v>0.04950048351498081</v>
       </c>
       <c r="H36" t="n">
-        <v>0.7270754716981123</v>
+        <v>0.4780704592104726</v>
       </c>
       <c r="I36" t="n">
-        <v>2.591981132075468</v>
+        <v>1.704292963125436</v>
       </c>
       <c r="J36" t="n">
-        <v>7.112594339622633</v>
+        <v>4.676710155246498</v>
       </c>
       <c r="K36" t="n">
-        <v>12.15655660377357</v>
+        <v>7.993242550750212</v>
       </c>
       <c r="L36" t="n">
-        <v>16.34599056603771</v>
+        <v>10.74790103688213</v>
       </c>
       <c r="M36" t="n">
-        <v>19.07499999999997</v>
+        <v>12.54229356430018</v>
       </c>
       <c r="N36" t="n">
-        <v>19.57985849056601</v>
+        <v>12.87425075418792</v>
       </c>
       <c r="O36" t="n">
-        <v>17.91174528301884</v>
+        <v>11.77742425104019</v>
       </c>
       <c r="P36" t="n">
-        <v>14.37575471698111</v>
+        <v>9.452421277522959</v>
       </c>
       <c r="Q36" t="n">
-        <v>9.609811320754705</v>
+        <v>6.318693299210532</v>
       </c>
       <c r="R36" t="n">
-        <v>4.674150943396222</v>
+        <v>3.073372125605564</v>
       </c>
       <c r="S36" t="n">
-        <v>1.398349056603771</v>
+        <v>0.9194497705523841</v>
       </c>
       <c r="T36" t="n">
-        <v>0.3034433962264145</v>
+        <v>0.1995216857467866</v>
       </c>
       <c r="U36" t="n">
-        <v>0.004952830188679241</v>
+        <v>0.003256610757564528</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -33724,49 +33724,49 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.06311475409836056</v>
+        <v>0.04149954254994795</v>
       </c>
       <c r="H37" t="n">
-        <v>0.5611475409836061</v>
+        <v>0.3689686601259011</v>
       </c>
       <c r="I37" t="n">
-        <v>1.898032786885244</v>
+        <v>1.248004425047526</v>
       </c>
       <c r="J37" t="n">
-        <v>4.462213114754091</v>
+        <v>2.93401765828132</v>
       </c>
       <c r="K37" t="n">
-        <v>7.332786885245889</v>
+        <v>4.821492307166679</v>
       </c>
       <c r="L37" t="n">
-        <v>9.383442622950806</v>
+        <v>6.169850171471354</v>
       </c>
       <c r="M37" t="n">
-        <v>9.893524590163919</v>
+        <v>6.505241928988658</v>
       </c>
       <c r="N37" t="n">
-        <v>9.658278688524582</v>
+        <v>6.350561815847948</v>
       </c>
       <c r="O37" t="n">
-        <v>8.920983606557368</v>
+        <v>5.865771705150827</v>
       </c>
       <c r="P37" t="n">
-        <v>7.633442622950805</v>
+        <v>5.019181037131885</v>
       </c>
       <c r="Q37" t="n">
-        <v>5.284999999999992</v>
+        <v>3.475020785705187</v>
       </c>
       <c r="R37" t="n">
-        <v>2.837868852459011</v>
+        <v>1.865970340473114</v>
       </c>
       <c r="S37" t="n">
-        <v>1.099918032786883</v>
+        <v>0.7232238460750018</v>
       </c>
       <c r="T37" t="n">
-        <v>0.2696721311475405</v>
+        <v>0.1773162272588685</v>
       </c>
       <c r="U37" t="n">
-        <v>0.003442622950819671</v>
+        <v>0.002263611411815345</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -33803,49 +33803,49 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1407035175879394</v>
+        <v>0.0925161113036756</v>
       </c>
       <c r="H38" t="n">
-        <v>1.440979899497485</v>
+        <v>0.9474806248887678</v>
       </c>
       <c r="I38" t="n">
-        <v>5.424472361809038</v>
+        <v>3.566727381034957</v>
       </c>
       <c r="J38" t="n">
-        <v>11.94203517587938</v>
+        <v>7.852189301760343</v>
       </c>
       <c r="K38" t="n">
-        <v>17.89801507537686</v>
+        <v>11.76839629324493</v>
       </c>
       <c r="L38" t="n">
-        <v>22.20407035175877</v>
+        <v>14.5997362345548</v>
       </c>
       <c r="M38" t="n">
-        <v>24.70630653266328</v>
+        <v>16.24501962895154</v>
       </c>
       <c r="N38" t="n">
-        <v>25.10608040201002</v>
+        <v>16.50788103019311</v>
       </c>
       <c r="O38" t="n">
-        <v>23.70695979899494</v>
+        <v>15.58792394841718</v>
       </c>
       <c r="P38" t="n">
-        <v>20.23334170854269</v>
+        <v>13.30393245060769</v>
       </c>
       <c r="Q38" t="n">
-        <v>15.1943969849246</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R38" t="n">
-        <v>8.838467336683406</v>
+        <v>5.811515176679517</v>
       </c>
       <c r="S38" t="n">
-        <v>3.206281407035172</v>
+        <v>2.10821088633251</v>
       </c>
       <c r="T38" t="n">
-        <v>0.615929648241205</v>
+        <v>0.4049892772318401</v>
       </c>
       <c r="U38" t="n">
-        <v>0.01125628140703515</v>
+        <v>0.007401288904294046</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -33882,49 +33882,49 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.07528301886792442</v>
+        <v>0.04950048351498081</v>
       </c>
       <c r="H39" t="n">
-        <v>0.7270754716981123</v>
+        <v>0.4780704592104726</v>
       </c>
       <c r="I39" t="n">
-        <v>2.591981132075468</v>
+        <v>1.704292963125436</v>
       </c>
       <c r="J39" t="n">
-        <v>7.112594339622633</v>
+        <v>4.676710155246498</v>
       </c>
       <c r="K39" t="n">
-        <v>12.15655660377357</v>
+        <v>7.993242550750212</v>
       </c>
       <c r="L39" t="n">
-        <v>16.34599056603771</v>
+        <v>10.74790103688213</v>
       </c>
       <c r="M39" t="n">
-        <v>19.07499999999997</v>
+        <v>12.54229356430018</v>
       </c>
       <c r="N39" t="n">
-        <v>19.57985849056601</v>
+        <v>12.87425075418792</v>
       </c>
       <c r="O39" t="n">
-        <v>17.91174528301884</v>
+        <v>11.77742425104019</v>
       </c>
       <c r="P39" t="n">
-        <v>14.37575471698111</v>
+        <v>9.452421277522959</v>
       </c>
       <c r="Q39" t="n">
-        <v>9.609811320754705</v>
+        <v>6.318693299210532</v>
       </c>
       <c r="R39" t="n">
-        <v>4.674150943396222</v>
+        <v>3.073372125605564</v>
       </c>
       <c r="S39" t="n">
-        <v>1.398349056603771</v>
+        <v>0.9194497705523841</v>
       </c>
       <c r="T39" t="n">
-        <v>0.3034433962264145</v>
+        <v>0.1995216857467866</v>
       </c>
       <c r="U39" t="n">
-        <v>0.004952830188679241</v>
+        <v>0.003256610757564528</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -33961,49 +33961,49 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.06311475409836056</v>
+        <v>0.04149954254994795</v>
       </c>
       <c r="H40" t="n">
-        <v>0.5611475409836061</v>
+        <v>0.3689686601259011</v>
       </c>
       <c r="I40" t="n">
-        <v>1.898032786885244</v>
+        <v>1.248004425047526</v>
       </c>
       <c r="J40" t="n">
-        <v>4.462213114754091</v>
+        <v>2.93401765828132</v>
       </c>
       <c r="K40" t="n">
-        <v>7.332786885245889</v>
+        <v>4.821492307166679</v>
       </c>
       <c r="L40" t="n">
-        <v>9.383442622950806</v>
+        <v>6.169850171471354</v>
       </c>
       <c r="M40" t="n">
-        <v>9.893524590163919</v>
+        <v>6.505241928988658</v>
       </c>
       <c r="N40" t="n">
-        <v>9.658278688524582</v>
+        <v>6.350561815847948</v>
       </c>
       <c r="O40" t="n">
-        <v>8.920983606557368</v>
+        <v>5.865771705150827</v>
       </c>
       <c r="P40" t="n">
-        <v>7.633442622950805</v>
+        <v>5.019181037131885</v>
       </c>
       <c r="Q40" t="n">
-        <v>5.284999999999992</v>
+        <v>3.475020785705187</v>
       </c>
       <c r="R40" t="n">
-        <v>2.837868852459011</v>
+        <v>1.865970340473114</v>
       </c>
       <c r="S40" t="n">
-        <v>1.099918032786883</v>
+        <v>0.7232238460750018</v>
       </c>
       <c r="T40" t="n">
-        <v>0.2696721311475405</v>
+        <v>0.1773162272588685</v>
       </c>
       <c r="U40" t="n">
-        <v>0.003442622950819671</v>
+        <v>0.002263611411815345</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -34040,49 +34040,49 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0.1407035175879394</v>
+        <v>0.0925161113036756</v>
       </c>
       <c r="H41" t="n">
-        <v>1.440979899497485</v>
+        <v>0.9474806248887678</v>
       </c>
       <c r="I41" t="n">
-        <v>5.424472361809038</v>
+        <v>3.566727381034957</v>
       </c>
       <c r="J41" t="n">
-        <v>11.94203517587938</v>
+        <v>7.852189301760343</v>
       </c>
       <c r="K41" t="n">
-        <v>17.89801507537686</v>
+        <v>11.76839629324493</v>
       </c>
       <c r="L41" t="n">
-        <v>22.20407035175877</v>
+        <v>14.5997362345548</v>
       </c>
       <c r="M41" t="n">
-        <v>24.70630653266328</v>
+        <v>16.24501962895154</v>
       </c>
       <c r="N41" t="n">
-        <v>25.10608040201002</v>
+        <v>16.50788103019311</v>
       </c>
       <c r="O41" t="n">
-        <v>23.70695979899494</v>
+        <v>15.58792394841718</v>
       </c>
       <c r="P41" t="n">
-        <v>20.23334170854269</v>
+        <v>13.30393245060769</v>
       </c>
       <c r="Q41" t="n">
-        <v>15.1943969849246</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R41" t="n">
-        <v>8.838467336683406</v>
+        <v>5.811515176679517</v>
       </c>
       <c r="S41" t="n">
-        <v>3.206281407035172</v>
+        <v>2.10821088633251</v>
       </c>
       <c r="T41" t="n">
-        <v>0.615929648241205</v>
+        <v>0.4049892772318401</v>
       </c>
       <c r="U41" t="n">
-        <v>0.01125628140703515</v>
+        <v>0.007401288904294046</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -34119,49 +34119,49 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.07528301886792442</v>
+        <v>0.04950048351498081</v>
       </c>
       <c r="H42" t="n">
-        <v>0.7270754716981123</v>
+        <v>0.4780704592104726</v>
       </c>
       <c r="I42" t="n">
-        <v>2.591981132075468</v>
+        <v>1.704292963125436</v>
       </c>
       <c r="J42" t="n">
-        <v>7.112594339622633</v>
+        <v>4.676710155246498</v>
       </c>
       <c r="K42" t="n">
-        <v>12.15655660377357</v>
+        <v>7.993242550750212</v>
       </c>
       <c r="L42" t="n">
-        <v>16.34599056603771</v>
+        <v>10.74790103688213</v>
       </c>
       <c r="M42" t="n">
-        <v>19.07499999999997</v>
+        <v>12.54229356430018</v>
       </c>
       <c r="N42" t="n">
-        <v>19.57985849056601</v>
+        <v>12.87425075418792</v>
       </c>
       <c r="O42" t="n">
-        <v>17.91174528301884</v>
+        <v>11.77742425104019</v>
       </c>
       <c r="P42" t="n">
-        <v>14.37575471698111</v>
+        <v>9.452421277522959</v>
       </c>
       <c r="Q42" t="n">
-        <v>9.609811320754705</v>
+        <v>6.318693299210532</v>
       </c>
       <c r="R42" t="n">
-        <v>4.674150943396222</v>
+        <v>3.073372125605564</v>
       </c>
       <c r="S42" t="n">
-        <v>1.398349056603771</v>
+        <v>0.9194497705523841</v>
       </c>
       <c r="T42" t="n">
-        <v>0.3034433962264145</v>
+        <v>0.1995216857467866</v>
       </c>
       <c r="U42" t="n">
-        <v>0.004952830188679241</v>
+        <v>0.003256610757564528</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -34198,49 +34198,49 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0.06311475409836056</v>
+        <v>0.04149954254994795</v>
       </c>
       <c r="H43" t="n">
-        <v>0.5611475409836061</v>
+        <v>0.3689686601259011</v>
       </c>
       <c r="I43" t="n">
-        <v>1.898032786885244</v>
+        <v>1.248004425047526</v>
       </c>
       <c r="J43" t="n">
-        <v>4.462213114754091</v>
+        <v>2.93401765828132</v>
       </c>
       <c r="K43" t="n">
-        <v>7.332786885245889</v>
+        <v>4.821492307166679</v>
       </c>
       <c r="L43" t="n">
-        <v>9.383442622950806</v>
+        <v>6.169850171471354</v>
       </c>
       <c r="M43" t="n">
-        <v>9.893524590163919</v>
+        <v>6.505241928988658</v>
       </c>
       <c r="N43" t="n">
-        <v>9.658278688524582</v>
+        <v>6.350561815847948</v>
       </c>
       <c r="O43" t="n">
-        <v>8.920983606557368</v>
+        <v>5.865771705150827</v>
       </c>
       <c r="P43" t="n">
-        <v>7.633442622950805</v>
+        <v>5.019181037131885</v>
       </c>
       <c r="Q43" t="n">
-        <v>5.284999999999992</v>
+        <v>3.475020785705187</v>
       </c>
       <c r="R43" t="n">
-        <v>2.837868852459011</v>
+        <v>1.865970340473114</v>
       </c>
       <c r="S43" t="n">
-        <v>1.099918032786883</v>
+        <v>0.7232238460750018</v>
       </c>
       <c r="T43" t="n">
-        <v>0.2696721311475405</v>
+        <v>0.1773162272588685</v>
       </c>
       <c r="U43" t="n">
-        <v>0.003442622950819671</v>
+        <v>0.002263611411815345</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -34277,49 +34277,49 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0.1407035175879394</v>
+        <v>0.0925161113036756</v>
       </c>
       <c r="H44" t="n">
-        <v>1.440979899497485</v>
+        <v>0.9474806248887678</v>
       </c>
       <c r="I44" t="n">
-        <v>5.424472361809038</v>
+        <v>3.566727381034957</v>
       </c>
       <c r="J44" t="n">
-        <v>11.94203517587938</v>
+        <v>7.852189301760343</v>
       </c>
       <c r="K44" t="n">
-        <v>17.89801507537686</v>
+        <v>11.76839629324493</v>
       </c>
       <c r="L44" t="n">
-        <v>22.20407035175877</v>
+        <v>14.5997362345548</v>
       </c>
       <c r="M44" t="n">
-        <v>24.70630653266328</v>
+        <v>16.24501962895154</v>
       </c>
       <c r="N44" t="n">
-        <v>25.10608040201002</v>
+        <v>16.50788103019311</v>
       </c>
       <c r="O44" t="n">
-        <v>23.70695979899494</v>
+        <v>15.58792394841718</v>
       </c>
       <c r="P44" t="n">
-        <v>20.23334170854269</v>
+        <v>13.30393245060769</v>
       </c>
       <c r="Q44" t="n">
-        <v>15.1943969849246</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R44" t="n">
-        <v>8.838467336683406</v>
+        <v>5.811515176679517</v>
       </c>
       <c r="S44" t="n">
-        <v>3.206281407035172</v>
+        <v>2.10821088633251</v>
       </c>
       <c r="T44" t="n">
-        <v>0.615929648241205</v>
+        <v>0.4049892772318401</v>
       </c>
       <c r="U44" t="n">
-        <v>0.01125628140703515</v>
+        <v>0.007401288904294046</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -34356,49 +34356,49 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0.07528301886792442</v>
+        <v>0.04950048351498081</v>
       </c>
       <c r="H45" t="n">
-        <v>0.7270754716981123</v>
+        <v>0.4780704592104726</v>
       </c>
       <c r="I45" t="n">
-        <v>2.591981132075468</v>
+        <v>1.704292963125436</v>
       </c>
       <c r="J45" t="n">
-        <v>7.112594339622633</v>
+        <v>4.676710155246498</v>
       </c>
       <c r="K45" t="n">
-        <v>12.15655660377357</v>
+        <v>7.993242550750212</v>
       </c>
       <c r="L45" t="n">
-        <v>16.34599056603771</v>
+        <v>10.74790103688213</v>
       </c>
       <c r="M45" t="n">
-        <v>19.07499999999997</v>
+        <v>12.54229356430018</v>
       </c>
       <c r="N45" t="n">
-        <v>19.57985849056601</v>
+        <v>12.87425075418792</v>
       </c>
       <c r="O45" t="n">
-        <v>17.91174528301884</v>
+        <v>11.77742425104019</v>
       </c>
       <c r="P45" t="n">
-        <v>14.37575471698111</v>
+        <v>9.452421277522959</v>
       </c>
       <c r="Q45" t="n">
-        <v>9.609811320754705</v>
+        <v>6.318693299210532</v>
       </c>
       <c r="R45" t="n">
-        <v>4.674150943396222</v>
+        <v>3.073372125605564</v>
       </c>
       <c r="S45" t="n">
-        <v>1.398349056603771</v>
+        <v>0.9194497705523841</v>
       </c>
       <c r="T45" t="n">
-        <v>0.3034433962264145</v>
+        <v>0.1995216857467866</v>
       </c>
       <c r="U45" t="n">
-        <v>0.004952830188679241</v>
+        <v>0.003256610757564528</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -34435,49 +34435,49 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0.06311475409836056</v>
+        <v>0.04149954254994795</v>
       </c>
       <c r="H46" t="n">
-        <v>0.5611475409836061</v>
+        <v>0.3689686601259011</v>
       </c>
       <c r="I46" t="n">
-        <v>1.898032786885244</v>
+        <v>1.248004425047526</v>
       </c>
       <c r="J46" t="n">
-        <v>4.462213114754091</v>
+        <v>2.93401765828132</v>
       </c>
       <c r="K46" t="n">
-        <v>7.332786885245889</v>
+        <v>4.821492307166679</v>
       </c>
       <c r="L46" t="n">
-        <v>9.383442622950806</v>
+        <v>6.169850171471354</v>
       </c>
       <c r="M46" t="n">
-        <v>9.893524590163919</v>
+        <v>6.505241928988658</v>
       </c>
       <c r="N46" t="n">
-        <v>9.658278688524582</v>
+        <v>6.350561815847948</v>
       </c>
       <c r="O46" t="n">
-        <v>8.920983606557368</v>
+        <v>5.865771705150827</v>
       </c>
       <c r="P46" t="n">
-        <v>7.633442622950805</v>
+        <v>5.019181037131885</v>
       </c>
       <c r="Q46" t="n">
-        <v>5.284999999999992</v>
+        <v>3.475020785705187</v>
       </c>
       <c r="R46" t="n">
-        <v>2.837868852459011</v>
+        <v>1.865970340473114</v>
       </c>
       <c r="S46" t="n">
-        <v>1.099918032786883</v>
+        <v>0.7232238460750018</v>
       </c>
       <c r="T46" t="n">
-        <v>0.2696721311475405</v>
+        <v>0.1773162272588685</v>
       </c>
       <c r="U46" t="n">
-        <v>0.003442622950819671</v>
+        <v>0.002263611411815345</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
